--- a/Supplemental Files/Table S4.xlsx
+++ b/Supplemental Files/Table S4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949A986E-719E-4065-A762-9C28BF26FB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E350E363-7DD8-4D00-B9FE-0317453D4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1901,6 +1901,1440 @@
   </si>
   <si>
     <t>HORVU.MOREX.r3.3HG0303530</t>
+  </si>
+  <si>
+    <t>n = indicates the number of terms in which a gene appears.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_log2FC = is the mean log2 fold-change across pairwise contrasts, preserving direction of change. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_abs_log2FC = is the largest absolute log2 fold-change observed across contrasts. </t>
+  </si>
+  <si>
+    <t>score = combines term frequency and effect size (log1p(n) × max_abs_log2FC).</t>
+  </si>
+  <si>
+    <t>Apyrase</t>
+  </si>
+  <si>
+    <t>Metallothionein</t>
+  </si>
+  <si>
+    <t>S-adenosyl-L-methionine-dependent methyltransferases superfamily protein</t>
+  </si>
+  <si>
+    <t>Protein TIC 62, chloroplastic</t>
+  </si>
+  <si>
+    <t>Heat shock 70 kDa protein</t>
+  </si>
+  <si>
+    <t>Pheophorbide a oxygenase, chloroplastic</t>
+  </si>
+  <si>
+    <t>3-ketoacyl-CoA synthase</t>
+  </si>
+  <si>
+    <t>Monocopper oxidase-like protein SKU5</t>
+  </si>
+  <si>
+    <t>Phototropic-responsive NPH3 family protein</t>
+  </si>
+  <si>
+    <t>BTB/POZ domain-containing protein</t>
+  </si>
+  <si>
+    <t>Gamma-glutamyltranspeptidase family protein</t>
+  </si>
+  <si>
+    <t>RING/U-box superfamily protein, putative</t>
+  </si>
+  <si>
+    <t>Auxin influx transporter</t>
+  </si>
+  <si>
+    <t>WAT1-related protein</t>
+  </si>
+  <si>
+    <t>Basic blue protein</t>
+  </si>
+  <si>
+    <t>GDP-mannose transporter</t>
+  </si>
+  <si>
+    <t>MADS-box transcription factor</t>
+  </si>
+  <si>
+    <t>Transporter-related family protein</t>
+  </si>
+  <si>
+    <t>F-box family protein-like</t>
+  </si>
+  <si>
+    <t>Leucine-rich repeat protein kinase family protein</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol transfer protein Sec14p</t>
+  </si>
+  <si>
+    <t>Vacuolar sorting receptor family protein</t>
+  </si>
+  <si>
+    <t>Potassium channel</t>
+  </si>
+  <si>
+    <t>Auxin-responsive protein</t>
+  </si>
+  <si>
+    <t>Protein NRT1/ PTR FAMILY 2.3</t>
+  </si>
+  <si>
+    <t>Protein argonaute</t>
+  </si>
+  <si>
+    <t>Ethylene-responsive transcription factor</t>
+  </si>
+  <si>
+    <t>Purple acid phosphatase</t>
+  </si>
+  <si>
+    <t>Kinase, putative</t>
+  </si>
+  <si>
+    <t>MYB-related protein</t>
+  </si>
+  <si>
+    <t>Myb transcription factor</t>
+  </si>
+  <si>
+    <t>Bifunctional uridylyltransferase/uridylyl-removing enzyme</t>
+  </si>
+  <si>
+    <t>NAC domain protein</t>
+  </si>
+  <si>
+    <t>YABBY protein</t>
+  </si>
+  <si>
+    <t>Ras-related protein Rab-25</t>
+  </si>
+  <si>
+    <t>Molybdenum cofactor sulfurase</t>
+  </si>
+  <si>
+    <t>Sec14p-like phosphatidylinositol transfer family protein</t>
+  </si>
+  <si>
+    <t>Non-specific serine/threonine protein kinase</t>
+  </si>
+  <si>
+    <t>Target of rapamycin complex 2 subunit MAPKAP1</t>
+  </si>
+  <si>
+    <t>4-coumarate: CoA ligase</t>
+  </si>
+  <si>
+    <t>Calcium-dependent protein kinase</t>
+  </si>
+  <si>
+    <t>Glutamate receptor</t>
+  </si>
+  <si>
+    <t>Reticulon-like protein</t>
+  </si>
+  <si>
+    <t>Beta-xylosidase, putative</t>
+  </si>
+  <si>
+    <t>Adenylyl-sulfate kinase</t>
+  </si>
+  <si>
+    <t>Protein ZINC INDUCED FACILITATOR-LIKE 1</t>
+  </si>
+  <si>
+    <t>Alpha-L-arabinofuranosidase 1</t>
+  </si>
+  <si>
+    <t>Ras-related protein</t>
+  </si>
+  <si>
+    <t>Methylsterol monooxygenase 1-2</t>
+  </si>
+  <si>
+    <t>E3 ubiquitin-protein ligase</t>
+  </si>
+  <si>
+    <t>GATA transcription factor</t>
+  </si>
+  <si>
+    <t>NAC domain-containing protein</t>
+  </si>
+  <si>
+    <t>Protein kinase family protein, putative, expressed</t>
+  </si>
+  <si>
+    <t>RNA-directed DNA polymerase (reverse transcriptase)-related family protein</t>
+  </si>
+  <si>
+    <t>Trichome birefringence-like protein</t>
+  </si>
+  <si>
+    <t>L-ascorbate oxidase-like protein</t>
+  </si>
+  <si>
+    <t>ATP-dependent zinc metalloprotease FtsH 1</t>
+  </si>
+  <si>
+    <t>basic helix-loop-helix (bHLH) DNA-binding superfamily protein</t>
+  </si>
+  <si>
+    <t>Caleosin</t>
+  </si>
+  <si>
+    <t>Kinesin-like protein</t>
+  </si>
+  <si>
+    <t>Catalase</t>
+  </si>
+  <si>
+    <t>Raffinose synthase family protein</t>
+  </si>
+  <si>
+    <t>Phospholipid-transporting ATPase</t>
+  </si>
+  <si>
+    <t>Calcium sensing receptor, chloroplastic</t>
+  </si>
+  <si>
+    <t>BZIP transcription factor</t>
+  </si>
+  <si>
+    <t>Histidine kinase</t>
+  </si>
+  <si>
+    <t>MADS box transcription factor</t>
+  </si>
+  <si>
+    <t>NAC domain containing protein 82</t>
+  </si>
+  <si>
+    <t>Pleiotropic drug resistance ABC transporter</t>
+  </si>
+  <si>
+    <t>Glyceraldehyde-3-phosphate dehydrogenase</t>
+  </si>
+  <si>
+    <t>Alpha/beta-Hydrolases superfamily protein, putative</t>
+  </si>
+  <si>
+    <t>XH/XS domain-containing family protein</t>
+  </si>
+  <si>
+    <t>Kinase family protein</t>
+  </si>
+  <si>
+    <t>tRNA-modifying protein YgfZ</t>
+  </si>
+  <si>
+    <t>Cytochrome f</t>
+  </si>
+  <si>
+    <t>Chloride channel protein</t>
+  </si>
+  <si>
+    <t>MYB-related transcription factor</t>
+  </si>
+  <si>
+    <t>Cellulose synthase-like protein</t>
+  </si>
+  <si>
+    <t>Receptor protein kinase</t>
+  </si>
+  <si>
+    <t>AT hook motif DNA-binding family protein</t>
+  </si>
+  <si>
+    <t>transcription factor-like protein</t>
+  </si>
+  <si>
+    <t>Acidic endochitinase</t>
+  </si>
+  <si>
+    <t>Protein NRT1/ PTR FAMILY 1.2</t>
+  </si>
+  <si>
+    <t>Protein NRT1/ PTR FAMILY 1.1</t>
+  </si>
+  <si>
+    <t>Argonaute</t>
+  </si>
+  <si>
+    <t>Yellow stripe-like transporter 1</t>
+  </si>
+  <si>
+    <t>Protein ETHYLENE INSENSITIVE 3</t>
+  </si>
+  <si>
+    <t>BEL1-like homeodomain protein</t>
+  </si>
+  <si>
+    <t>Myosin family protein, putative, expressed</t>
+  </si>
+  <si>
+    <t>transmembrane protein</t>
+  </si>
+  <si>
+    <t>MYB transcription factor</t>
+  </si>
+  <si>
+    <t>Zinc-finger homeodomain protein 1</t>
+  </si>
+  <si>
+    <t>Nuclear transcription factor Y subunit</t>
+  </si>
+  <si>
+    <t>F5O11.10 isoform 1</t>
+  </si>
+  <si>
+    <t>TBC1 domain family member</t>
+  </si>
+  <si>
+    <t>Aspartic proteinase Asp1</t>
+  </si>
+  <si>
+    <t>MLO-like protein</t>
+  </si>
+  <si>
+    <t>Callose synthase-like protein</t>
+  </si>
+  <si>
+    <t>Phosphate translocator</t>
+  </si>
+  <si>
+    <t>Protein IQ-DOMAIN 1</t>
+  </si>
+  <si>
+    <t>Nodulin-like / Major Facilitator Superfamily protein</t>
+  </si>
+  <si>
+    <t>Heat shock transcription factor</t>
+  </si>
+  <si>
+    <t>Leucine-rich repeat receptor-like protein kinase</t>
+  </si>
+  <si>
+    <t>Protein DETOXIFICATION</t>
+  </si>
+  <si>
+    <t>Protodermal factor 1</t>
+  </si>
+  <si>
+    <t>Syntaxin, putative</t>
+  </si>
+  <si>
+    <t>ABC transporter B family protein</t>
+  </si>
+  <si>
+    <t>RAN GTPase activating protein 2</t>
+  </si>
+  <si>
+    <t>Receptor protein kinase, putative</t>
+  </si>
+  <si>
+    <t>Transcription factor</t>
+  </si>
+  <si>
+    <t>Protein lateral root primordium 1</t>
+  </si>
+  <si>
+    <t>Cytochrome b561 domain-containing protein</t>
+  </si>
+  <si>
+    <t>Heme oxygenase 1</t>
+  </si>
+  <si>
+    <t>Peptide transporter</t>
+  </si>
+  <si>
+    <t>Peroxidase</t>
+  </si>
+  <si>
+    <t>Two-component response regulator</t>
+  </si>
+  <si>
+    <t>Phosphoenolpyruvate carboxylase</t>
+  </si>
+  <si>
+    <t>Protein kinase family protein</t>
+  </si>
+  <si>
+    <t>Type I inositol-1,4,5-trisphosphate 5-phosphatase 1</t>
+  </si>
+  <si>
+    <t>O-acyltransferase</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol N-acetyglucosaminlytransferase subunit P-like protein</t>
+  </si>
+  <si>
+    <t>carboxyl-terminal peptidase, putative (DUF239)</t>
+  </si>
+  <si>
+    <t>Carboxypeptidase</t>
+  </si>
+  <si>
+    <t>Beta-fructofuranosidase, insoluble protein</t>
+  </si>
+  <si>
+    <t>Choline/ethanolamine kinase</t>
+  </si>
+  <si>
+    <t>Amino acid transporter-like protein</t>
+  </si>
+  <si>
+    <t>Zeaxanthin epoxidase, chloroplastic</t>
+  </si>
+  <si>
+    <t>ACT domain containing protein, expressed</t>
+  </si>
+  <si>
+    <t>Leucine-rich repeat receptor-like protein kinase family protein, putative</t>
+  </si>
+  <si>
+    <t>Leucine-rich repeat receptor-like protein kinase family protein</t>
+  </si>
+  <si>
+    <t>ABC subfamily C transporter</t>
+  </si>
+  <si>
+    <t>Zinc finger CCCH domain-containing protein 4</t>
+  </si>
+  <si>
+    <t>Ethylene-responsive transcription factor, putative</t>
+  </si>
+  <si>
+    <t>Xyloglucan galactosyltransferase KATAMARI1, putative</t>
+  </si>
+  <si>
+    <t>Sugar phosphate/phosphate translocator</t>
+  </si>
+  <si>
+    <t>Fructose-1,6-bisphosphatase class 1</t>
+  </si>
+  <si>
+    <t>Mitotic checkpoint protein bub3.1</t>
+  </si>
+  <si>
+    <t>Transport inhibitor response 1-like protein</t>
+  </si>
+  <si>
+    <t>Signal peptide peptidase family protein</t>
+  </si>
+  <si>
+    <t>Nucleosome assembly protein 1-like 1</t>
+  </si>
+  <si>
+    <t>Amino acid permease</t>
+  </si>
+  <si>
+    <t>Phospholipase A1</t>
+  </si>
+  <si>
+    <t>Glucan endo-1,3-beta-glucosidase, putative</t>
+  </si>
+  <si>
+    <t>Sugar transporter, putative</t>
+  </si>
+  <si>
+    <t>SPX domain-containing protein</t>
+  </si>
+  <si>
+    <t>Dof zinc finger protein</t>
+  </si>
+  <si>
+    <t>F-box protein</t>
+  </si>
+  <si>
+    <t>Phosphoinositide phospholipase C</t>
+  </si>
+  <si>
+    <t>Scarecrow transcription factor family protein</t>
+  </si>
+  <si>
+    <t>Chlorophyllide a oxygenase, chloroplastic</t>
+  </si>
+  <si>
+    <t>Amino acid permease family protein</t>
+  </si>
+  <si>
+    <t>Phenylalanine ammonia-lyase</t>
+  </si>
+  <si>
+    <t>Long-chain-fatty-acid CoA ligase, putative</t>
+  </si>
+  <si>
+    <t>DNA-binding protein SMUBP-2</t>
+  </si>
+  <si>
+    <t>Acetyl-coenzyme A synthetase</t>
+  </si>
+  <si>
+    <t>Germin-like protein 1</t>
+  </si>
+  <si>
+    <t>UPF0301 protein</t>
+  </si>
+  <si>
+    <t>2-phosphoglycerate kinase-related family protein</t>
+  </si>
+  <si>
+    <t>Protein PLASTID MOVEMENT IMPAIRED 2</t>
+  </si>
+  <si>
+    <t>Serine/Threonine-kinase WNK (WNK)-like protein</t>
+  </si>
+  <si>
+    <t>Glycerol kinase</t>
+  </si>
+  <si>
+    <t>Glutathione S-transferase</t>
+  </si>
+  <si>
+    <t>Calcium-dependent lipid-binding domain-containing protein</t>
+  </si>
+  <si>
+    <t>Glycosyltransferase</t>
+  </si>
+  <si>
+    <t>Glutamate decarboxylase</t>
+  </si>
+  <si>
+    <t>RING finger protein</t>
+  </si>
+  <si>
+    <t>CDT1-like protein a, chloroplastic</t>
+  </si>
+  <si>
+    <t>E3 ubiquitin-protein ligase RGLG2</t>
+  </si>
+  <si>
+    <t>Calcium-binding EF-hand family protein</t>
+  </si>
+  <si>
+    <t>Basic helix-loop-helix (BHLH) Transcription Factor</t>
+  </si>
+  <si>
+    <t>D-3-phosphoglycerate dehydrogenase</t>
+  </si>
+  <si>
+    <t>Receptor-like kinase</t>
+  </si>
+  <si>
+    <t>Orotate phosphoribosyltransferase, Orotidine-5'-phosphate decarboxylase</t>
+  </si>
+  <si>
+    <t>Proline transporter</t>
+  </si>
+  <si>
+    <t>ENTH/ANTH/VHS superfamily protein</t>
+  </si>
+  <si>
+    <t>U-box domain-containing protein</t>
+  </si>
+  <si>
+    <t>Endo-1,4-beta-xylanase, putative, expressed</t>
+  </si>
+  <si>
+    <t>Vesicle-associated 1-1-like protein</t>
+  </si>
+  <si>
+    <t>Chitinase-like protein</t>
+  </si>
+  <si>
+    <t>Calpain-like protein</t>
+  </si>
+  <si>
+    <t>Basic helix-loop-helix transcription factor</t>
+  </si>
+  <si>
+    <t>RING/U-box superfamily protein</t>
+  </si>
+  <si>
+    <t>Core-2/I-branching beta-1,6-N-acetylglucosaminyltransferase family protein</t>
+  </si>
+  <si>
+    <t>Receptor-like protein kinase</t>
+  </si>
+  <si>
+    <t>Lipase</t>
+  </si>
+  <si>
+    <t>LIGHT-DEPENDENT SHORT HYPOCOTYLS-like protein (DUF640)</t>
+  </si>
+  <si>
+    <t>Mitochondrial carrier protein, putative</t>
+  </si>
+  <si>
+    <t>TBC1 domain family member-like protein</t>
+  </si>
+  <si>
+    <t>Protein ABIL1</t>
+  </si>
+  <si>
+    <t>Fatty-acid desaturase</t>
+  </si>
+  <si>
+    <t>Glutamyl-tRNA reductase</t>
+  </si>
+  <si>
+    <t>Seipin</t>
+  </si>
+  <si>
+    <t>Pirin-like protein</t>
+  </si>
+  <si>
+    <t>Sphingoid base hydroxylase 2</t>
+  </si>
+  <si>
+    <t>Kinase-like protein</t>
+  </si>
+  <si>
+    <t>Basic helix loop helix (BHLH) family transcription factor</t>
+  </si>
+  <si>
+    <t>Subtilisin protease</t>
+  </si>
+  <si>
+    <t>Exocyst complex component, putative</t>
+  </si>
+  <si>
+    <t>WEB family protein, chloroplastic</t>
+  </si>
+  <si>
+    <t>Endo-1,3(4)-beta-glucanase 1</t>
+  </si>
+  <si>
+    <t>Aldose 1-epimerase-like</t>
+  </si>
+  <si>
+    <t>Tubby-like F-box protein</t>
+  </si>
+  <si>
+    <t>Regulator of chromosome condensation (RCC1) family with FYVE zinc finger domain-containing protein</t>
+  </si>
+  <si>
+    <t>Dicer-like protein 3</t>
+  </si>
+  <si>
+    <t>C2 calcium/lipid-binding and GRAM domain protein</t>
+  </si>
+  <si>
+    <t>Acetyl-CoA carboxylase</t>
+  </si>
+  <si>
+    <t>AGAMOUS MADS box factor transcription factor</t>
+  </si>
+  <si>
+    <t>glucan synthase-like 9</t>
+  </si>
+  <si>
+    <t>PPPDE thiol peptidase family protein, putative</t>
+  </si>
+  <si>
+    <t>Acetolactate synthase</t>
+  </si>
+  <si>
+    <t>AP2/B3 transcription factor family protein</t>
+  </si>
+  <si>
+    <t>Phosphate transporter</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol 3,4,5-trisphosphate 3-phosphatase and dual-specificity protein phosphatase PTEN</t>
+  </si>
+  <si>
+    <t>Zinc transporter</t>
+  </si>
+  <si>
+    <t>Metal transporter, putative</t>
+  </si>
+  <si>
+    <t>Pyruvate dehydrogenase E1 component alpha subunit</t>
+  </si>
+  <si>
+    <t>Nitrate transporter 1.1</t>
+  </si>
+  <si>
+    <t>Serine/threonine-protein phosphatase</t>
+  </si>
+  <si>
+    <t>Ribulose-phosphate 3-epimerase</t>
+  </si>
+  <si>
+    <t>transmembrane protein, putative (DUF679 domain membrane protein 2)</t>
+  </si>
+  <si>
+    <t>Calmodulin-binding transcription activator</t>
+  </si>
+  <si>
+    <t>Homeobox protein, putative</t>
+  </si>
+  <si>
+    <t>Transducin/WD40 repeat-like superfamily protein</t>
+  </si>
+  <si>
+    <t>Subtilisin-like protease</t>
+  </si>
+  <si>
+    <t>VQ motif family protein</t>
+  </si>
+  <si>
+    <t>CoA ligase</t>
+  </si>
+  <si>
+    <t>Guanylyl cyclase</t>
+  </si>
+  <si>
+    <t>Zinc finger-homeodomain protein 1</t>
+  </si>
+  <si>
+    <t>Protein strawberry notch-like protein 1</t>
+  </si>
+  <si>
+    <t>Protein DA1-related 1</t>
+  </si>
+  <si>
+    <t>LysM domain-containing GPI-anchored protein 1</t>
+  </si>
+  <si>
+    <t>Lactation elevated protein 1</t>
+  </si>
+  <si>
+    <t>Kelch repeat protein, putative</t>
+  </si>
+  <si>
+    <t>Aldo/keto reductase family-like protein</t>
+  </si>
+  <si>
+    <t>DNA polymerase delta small subunit</t>
+  </si>
+  <si>
+    <t>Leucine-rich repeat receptor-like kinase</t>
+  </si>
+  <si>
+    <t>Major facilitator superfamily transporter</t>
+  </si>
+  <si>
+    <t>Ring finger protein, putative</t>
+  </si>
+  <si>
+    <t>Methyltransferase</t>
+  </si>
+  <si>
+    <t>protein kinase family protein</t>
+  </si>
+  <si>
+    <t>E3 ubiquitin-protein ligase RGLG2-like protein</t>
+  </si>
+  <si>
+    <t>ABC transporter, putative</t>
+  </si>
+  <si>
+    <t>Malic enzyme</t>
+  </si>
+  <si>
+    <t>Calmodulin</t>
+  </si>
+  <si>
+    <t>Protein kinase</t>
+  </si>
+  <si>
+    <t>Ubiquitin-conjugating enzyme, E2</t>
+  </si>
+  <si>
+    <t>Ankyrin repeat protein-like</t>
+  </si>
+  <si>
+    <t>WEAK movement UNDER BLUE LIGHT-like protein</t>
+  </si>
+  <si>
+    <t>Mechanosensitive ion channel family protein</t>
+  </si>
+  <si>
+    <t>Synaptotagmin-5</t>
+  </si>
+  <si>
+    <t>ATP-dependent RNA helicase</t>
+  </si>
+  <si>
+    <t>Syntaxin</t>
+  </si>
+  <si>
+    <t>Pantothenate kinase family protein</t>
+  </si>
+  <si>
+    <t>Photosystem II reaction center PsbP family protein</t>
+  </si>
+  <si>
+    <t>Zinc finger (C3HC4-type RING finger) family protein</t>
+  </si>
+  <si>
+    <t>6-phosphogluconate dehydrogenase-like protein</t>
+  </si>
+  <si>
+    <t>Hexosyltransferase</t>
+  </si>
+  <si>
+    <t>C2 and GRAM domain-containing protein</t>
+  </si>
+  <si>
+    <t>Glycosyltransferases</t>
+  </si>
+  <si>
+    <t>Protein phosphatase 2C</t>
+  </si>
+  <si>
+    <t>Cryptochrome-1</t>
+  </si>
+  <si>
+    <t>Phosphoinositide phosphatase family protein</t>
+  </si>
+  <si>
+    <t>GATA transcription factor, putative</t>
+  </si>
+  <si>
+    <t>1,4-alpha-glucan branching enzyme GlgB</t>
+  </si>
+  <si>
+    <t>Glutamate synthase, putative</t>
+  </si>
+  <si>
+    <t>GPI inositol-deacylase</t>
+  </si>
+  <si>
+    <t>Glutathione-regulated potassium-efflux system protein</t>
+  </si>
+  <si>
+    <t>IQ domain-containing protein</t>
+  </si>
+  <si>
+    <t>Interactor of constitutive active ROPs 2, chloroplastic</t>
+  </si>
+  <si>
+    <t>Histone-lysine N-methyltransferase</t>
+  </si>
+  <si>
+    <t>CC-NBS-LRR family disease resistance protein</t>
+  </si>
+  <si>
+    <t>Xyloglucan alpha-1,6-xylosyltransferase</t>
+  </si>
+  <si>
+    <t>Ornithine decarboxylase</t>
+  </si>
+  <si>
+    <t>H/ACA ribonucleoprotein complex non-core subunit NAF1</t>
+  </si>
+  <si>
+    <t>Sucrose synthase</t>
+  </si>
+  <si>
+    <t>Calcium-transporting ATPase</t>
+  </si>
+  <si>
+    <t>Dolichol-phosphate mannosyltransferase, putative, expressed</t>
+  </si>
+  <si>
+    <t>UDP-glucose 4-epimerase, putative</t>
+  </si>
+  <si>
+    <t>Cytochrome P450, putative</t>
+  </si>
+  <si>
+    <t>Heparanase</t>
+  </si>
+  <si>
+    <t>Ankyrin repeat and BTB/POZ domain protein</t>
+  </si>
+  <si>
+    <t>Ankyrin repeat and BTB/POZ domain-containing protein 1</t>
+  </si>
+  <si>
+    <t>Vesicle-associated protein 1-1</t>
+  </si>
+  <si>
+    <t>Profilin</t>
+  </si>
+  <si>
+    <t>60S ribosomal export protein NMD3</t>
+  </si>
+  <si>
+    <t>Mitochondrial carrier family</t>
+  </si>
+  <si>
+    <t>GTP cyclohydrolase II/3,4-dihydroxy-2-butanone 4-phosphate synthase</t>
+  </si>
+  <si>
+    <t>Cyclin</t>
+  </si>
+  <si>
+    <t>Homeobox-leucine zipper family protein</t>
+  </si>
+  <si>
+    <t>RING/FYVE/PHD zinc finger superfamily protein</t>
+  </si>
+  <si>
+    <t>Carboxymethylenebutenolidase-like protein</t>
+  </si>
+  <si>
+    <t>TCP transcription factor</t>
+  </si>
+  <si>
+    <t>transcription repressor</t>
+  </si>
+  <si>
+    <t>Pumilio-like protein</t>
+  </si>
+  <si>
+    <t>Exocyst complex component EXO70A1</t>
+  </si>
+  <si>
+    <t>Argonaute family protein</t>
+  </si>
+  <si>
+    <t>Respiratory burst oxidase, putative</t>
+  </si>
+  <si>
+    <t>Homeobox protein BEL1-like protein</t>
+  </si>
+  <si>
+    <t>Cytochrome P450 family protein</t>
+  </si>
+  <si>
+    <t>2,3-bisphosphoglycerate-dependent phosphoglycerate mutase</t>
+  </si>
+  <si>
+    <t>RNA binding protein, putative</t>
+  </si>
+  <si>
+    <t>GEM-like protein 1</t>
+  </si>
+  <si>
+    <t>AT hook motif DNA-binding family protein, putative</t>
+  </si>
+  <si>
+    <t>Syntaxin protein</t>
+  </si>
+  <si>
+    <t>Leucine-rich repeat-containing protein</t>
+  </si>
+  <si>
+    <t>Mitochondrial carrier protein-like</t>
+  </si>
+  <si>
+    <t>Auxin efflux carrier family protein</t>
+  </si>
+  <si>
+    <t>Carotenoid isomerase, putative, expressed</t>
+  </si>
+  <si>
+    <t>Exostosin-2</t>
+  </si>
+  <si>
+    <t>Poly [ADP-ribose] polymerase</t>
+  </si>
+  <si>
+    <t>TBC1 domain family member 8B</t>
+  </si>
+  <si>
+    <t>DUF4228 domain protein</t>
+  </si>
+  <si>
+    <t>Coenzyme Q-binding protein COQ10, mitochondrial</t>
+  </si>
+  <si>
+    <t>Protein phosphatase 2c, putative</t>
+  </si>
+  <si>
+    <t>Acetyltransferase component of pyruvate dehydrogenase complex</t>
+  </si>
+  <si>
+    <t>Lorelei-like-GPI-anchored protein</t>
+  </si>
+  <si>
+    <t>DUF936 family protein</t>
+  </si>
+  <si>
+    <t>Respiratory burst oxidase homolog</t>
+  </si>
+  <si>
+    <t>Acyl-CoA-binding domain-containing protein 4</t>
+  </si>
+  <si>
+    <t>Presequence protease, mitochondrial</t>
+  </si>
+  <si>
+    <t>Alkaline/neutral invertase</t>
+  </si>
+  <si>
+    <t>Zinc finger protein</t>
+  </si>
+  <si>
+    <t>Jasmonate ZIM domain-containing protein</t>
+  </si>
+  <si>
+    <t>Receptor kinase</t>
+  </si>
+  <si>
+    <t>Endosomal targeting BRO1-like domain-containing protein</t>
+  </si>
+  <si>
+    <t>Dihydrolipoyl dehydrogenase</t>
+  </si>
+  <si>
+    <t>D-glycerate dehydrogenase/hydroxypyruvate reductase</t>
+  </si>
+  <si>
+    <t>Geranylgeranyl pyrophosphate synthase</t>
+  </si>
+  <si>
+    <t>Inositol-pentakisphosphate 2-kinase</t>
+  </si>
+  <si>
+    <t>Cytochrome b561 and DOMON domain-containing protein</t>
+  </si>
+  <si>
+    <t>Auxin response factor</t>
+  </si>
+  <si>
+    <t>BES1/BZR1 homolog 1</t>
+  </si>
+  <si>
+    <t>Chaperone protein dnaJ, putative</t>
+  </si>
+  <si>
+    <t>Alpha-glucosidase</t>
+  </si>
+  <si>
+    <t>Serine acetyltransferase</t>
+  </si>
+  <si>
+    <t>N-acetyltransferase, putative, expressed</t>
+  </si>
+  <si>
+    <t>Protein trichome birefringence</t>
+  </si>
+  <si>
+    <t>Sodium/hydrogen exchanger</t>
+  </si>
+  <si>
+    <t>Copper transporter family protein</t>
+  </si>
+  <si>
+    <t>Protein kinase 2A, chloroplastic</t>
+  </si>
+  <si>
+    <t>Eukaryotic aspartyl protease family protein</t>
+  </si>
+  <si>
+    <t>Phosphatidylcholine:diacylglycerol cholinephosphotransferase 1</t>
+  </si>
+  <si>
+    <t>Oxygen-dependent coproporphyrinogen-III oxidase</t>
+  </si>
+  <si>
+    <t>Programmed cell death-4</t>
+  </si>
+  <si>
+    <t>PsbP family protein, expressed</t>
+  </si>
+  <si>
+    <t>Protein kinase, putative</t>
+  </si>
+  <si>
+    <t>50S ribosomal protein L19, putative</t>
+  </si>
+  <si>
+    <t>ATP-dependent Clp protease ATP-binding subunit ClpB</t>
+  </si>
+  <si>
+    <t>Potassium efflux antiporter</t>
+  </si>
+  <si>
+    <t>Alpha/beta-Hydrolases superfamily protein</t>
+  </si>
+  <si>
+    <t>Terpene cyclase/mutase family member</t>
+  </si>
+  <si>
+    <t>WRKY transcription factor</t>
+  </si>
+  <si>
+    <t>Membrane protein of ER body-like protein</t>
+  </si>
+  <si>
+    <t>Membrane protein of er body-like protein</t>
+  </si>
+  <si>
+    <t>Cytochrome P450-like protein</t>
+  </si>
+  <si>
+    <t>Transcription elongation factor SPT5</t>
+  </si>
+  <si>
+    <t>Ubiquitin-conjugating enzyme E2</t>
+  </si>
+  <si>
+    <t>PAX-interacting protein 1</t>
+  </si>
+  <si>
+    <t>transmembrane protein, putative (DUF288)</t>
+  </si>
+  <si>
+    <t>Hedgehog-interacting-like protein</t>
+  </si>
+  <si>
+    <t>Citrate synthase</t>
+  </si>
+  <si>
+    <t>Cellulose synthase</t>
+  </si>
+  <si>
+    <t>Thymidine kinase</t>
+  </si>
+  <si>
+    <t>ORMDL family protein-like</t>
+  </si>
+  <si>
+    <t>Zinc finger SWIM domain-containing protein 7</t>
+  </si>
+  <si>
+    <t>Brevis radix-like protein</t>
+  </si>
+  <si>
+    <t>2-oxoglutarate (2OG) and Fe(II)-dependent oxygenase superfamily protein</t>
+  </si>
+  <si>
+    <t>FAD-binding Berberine family protein, putative</t>
+  </si>
+  <si>
+    <t>Resistance to phytophthora 1 protein</t>
+  </si>
+  <si>
+    <t>SPX domain-containing family protein</t>
+  </si>
+  <si>
+    <t>UDP-glucose pyrophosphorylase</t>
+  </si>
+  <si>
+    <t>Zinc finger CCCH domain protein</t>
+  </si>
+  <si>
+    <t>Uridylate kinase</t>
+  </si>
+  <si>
+    <t>Indole-3-acetic acid-amido synthetase GH3.3</t>
+  </si>
+  <si>
+    <t>Transcription factor, putative</t>
+  </si>
+  <si>
+    <t>Transporter</t>
+  </si>
+  <si>
+    <t>Gamma interferon inducible lysosomal thiol reductase family protein, expressed</t>
+  </si>
+  <si>
+    <t>Solanesyl diphosphate synthase family protein</t>
+  </si>
+  <si>
+    <t>Nudix hydrolase-like protein</t>
+  </si>
+  <si>
+    <t>Transaldolase</t>
+  </si>
+  <si>
+    <t>Serine/threonine protein phosphatase 2A regulatory subunit B</t>
+  </si>
+  <si>
+    <t>Glucose-1-phosphate adenylyltransferase</t>
+  </si>
+  <si>
+    <t>Leucine-rich repeat (LRR) family protein</t>
+  </si>
+  <si>
+    <t>Respiratory burst oxidase</t>
+  </si>
+  <si>
+    <t>Carbon catabolite repressor protein 4</t>
+  </si>
+  <si>
+    <t>Protein REVERSION-TO-ETHYLENE SENSITIVITY1</t>
+  </si>
+  <si>
+    <t>Acyl-CoA N-acyltransferase with RING/FYVE/PHD-type zinc finger protein</t>
+  </si>
+  <si>
+    <t>Trihelix transcription factor</t>
+  </si>
+  <si>
+    <t>F-box/kelch-repeat protein</t>
+  </si>
+  <si>
+    <t>DNA/RNA helicase protein</t>
+  </si>
+  <si>
+    <t>Acyl-CoA ligase-like</t>
+  </si>
+  <si>
+    <t>1-aminocyclopropane-1-carboxylate synthase</t>
+  </si>
+  <si>
+    <t>F-box-like protein</t>
+  </si>
+  <si>
+    <t>2-oxoglutarate-dependent dioxygenase</t>
+  </si>
+  <si>
+    <t>electron transporter, putative (Protein of unknown function, DUF547)</t>
+  </si>
+  <si>
+    <t>PI-PLC X domain-containing protein</t>
+  </si>
+  <si>
+    <t>Protein phosphatase 2C containing protein</t>
+  </si>
+  <si>
+    <t>Calcium dependent protein kinase</t>
+  </si>
+  <si>
+    <t>Cytokinin oxidase/dehydrogenase</t>
+  </si>
+  <si>
+    <t>Malonyl CoA-acyl carrier protein transacylase containing protein, expressed</t>
+  </si>
+  <si>
+    <t>BTB/POZ and MATH domain-containing protein 2</t>
+  </si>
+  <si>
+    <t>Aspartate aminotransferase</t>
+  </si>
+  <si>
+    <t>Glycerol-3-phosphate dehydrogenase [NAD(+)]</t>
+  </si>
+  <si>
+    <t>Vacuole membrane-like protein</t>
+  </si>
+  <si>
+    <t>Alpha-glucan water dikinase</t>
+  </si>
+  <si>
+    <t>Chorismate mutase</t>
+  </si>
+  <si>
+    <t>GRAM domain-containing protein / ABA-responsive</t>
+  </si>
+  <si>
+    <t>Beta-carotene hydroxylase, putative, expressed</t>
+  </si>
+  <si>
+    <t>ATP-dependent chaperone ClpB</t>
+  </si>
+  <si>
+    <t>F-box protein PP2-A13</t>
+  </si>
+  <si>
+    <t>UPF0496 protein</t>
+  </si>
+  <si>
+    <t>Mitochondrial carrier protein</t>
+  </si>
+  <si>
+    <t>Lysine-specific demethylase</t>
+  </si>
+  <si>
+    <t>Eukaryotic translation initiation factor 4G</t>
+  </si>
+  <si>
+    <t>Rho GTPase-activating protein</t>
+  </si>
+  <si>
+    <t>FAD binding protein</t>
+  </si>
+  <si>
+    <t>F-box family protein</t>
+  </si>
+  <si>
+    <t>TOX high mobility group box protein, putative (DUF1635)</t>
+  </si>
+  <si>
+    <t>Microtubule associated family protein</t>
+  </si>
+  <si>
+    <t>Tryptophan aminotransferase</t>
+  </si>
+  <si>
+    <t>Pyridoxamine 5-phosphate oxidase family protein</t>
+  </si>
+  <si>
+    <t>Translation initiation factor IF-2</t>
+  </si>
+  <si>
+    <t>Glutamate dehydrogenase</t>
+  </si>
+  <si>
+    <t>Calcineurin-like metallo-phosphoesterase superfamily</t>
+  </si>
+  <si>
+    <t>ARM repeat superfamily protein</t>
+  </si>
+  <si>
+    <t>Glucose-6-phosphate 1-dehydrogenase</t>
+  </si>
+  <si>
+    <t>ABC transporter ATP-binding protein</t>
+  </si>
+  <si>
+    <t>Mitochondrial import inner membrane translocase subunit Tim10 B</t>
+  </si>
+  <si>
+    <t>CAS1 domain-containing protein 1</t>
+  </si>
+  <si>
+    <t>Formin-like protein</t>
+  </si>
+  <si>
+    <t>Coiled-coil domain-containing 90B, mitochondrial</t>
+  </si>
+  <si>
+    <t>CRS2-associated factor 1, chloroplastic</t>
+  </si>
+  <si>
+    <t>Linalool synthase</t>
+  </si>
+  <si>
+    <t>Ferredoxin--NADP reductase</t>
+  </si>
+  <si>
+    <t>Kelch repeat-containing protein</t>
+  </si>
+  <si>
+    <t>Uridine kinase</t>
+  </si>
+  <si>
+    <t>Set1/Ash2 histone methyltransferase complex subunit ASH2</t>
+  </si>
+  <si>
+    <t>Carotenoid cleavage dioxygenase</t>
+  </si>
+  <si>
+    <t>Elongation factor 4</t>
+  </si>
+  <si>
+    <t>Glycogen synthase</t>
+  </si>
+  <si>
+    <t>Flap endonuclease 1</t>
+  </si>
+  <si>
+    <t>DNA mismatch repair protein mutS</t>
+  </si>
+  <si>
+    <t>GDT1-like protein</t>
+  </si>
+  <si>
+    <t>Mediator of RNA polymerase II transcription subunit 16</t>
+  </si>
+  <si>
+    <t>B3 domain-containing protein</t>
+  </si>
+  <si>
+    <t>RNA ligase/cyclic nucleotide phosphodiesterase family protein</t>
+  </si>
+  <si>
+    <t>Phosphoglycerate kinase</t>
+  </si>
+  <si>
+    <t>methyl esterase 12</t>
+  </si>
+  <si>
+    <t>Polyol transporter</t>
+  </si>
+  <si>
+    <t>ELMO domain containing protein</t>
+  </si>
+  <si>
+    <t>Tobamovirus multiplication protein</t>
+  </si>
+  <si>
+    <t>Dual specificity protein phosphatase family protein</t>
+  </si>
+  <si>
+    <t>Xyloglucan galactosyltransferase KATAMARI1-like protein</t>
+  </si>
+  <si>
+    <t>U-box domain-containing protein 4</t>
+  </si>
+  <si>
+    <t>Sphingosine-1-phosphate phosphatase 1</t>
+  </si>
+  <si>
+    <t>Dual specificity phosphatase family protein</t>
+  </si>
+  <si>
+    <t>Hsp70 nucleotide exchange factor fes1</t>
+  </si>
+  <si>
+    <t>Oxysterol-binding family protein</t>
+  </si>
+  <si>
+    <t>Protein SIP5</t>
+  </si>
+  <si>
+    <t>3-ketodihydrosphingosine reductase</t>
+  </si>
+  <si>
+    <t>3(2),5-bisphosphate nucleotidase HAL2</t>
+  </si>
+  <si>
+    <t>Chalcone--flavonone isomerase</t>
+  </si>
+  <si>
+    <t>Oxysterol-binding protein</t>
+  </si>
+  <si>
+    <t>4-alpha-glucanotransferase</t>
+  </si>
+  <si>
+    <t>ATP-dependent protease La (LON) domain-containing protein</t>
+  </si>
+  <si>
+    <t>High mobility group family protein</t>
+  </si>
+  <si>
+    <t>Flavonol synthase</t>
+  </si>
+  <si>
+    <t>Transporter family protein</t>
+  </si>
+  <si>
+    <t>TATA-binding protein associated factor-like protein</t>
+  </si>
+  <si>
+    <t>Ubiquinone biosynthesis O-methyltransferase</t>
+  </si>
+  <si>
+    <t>Flavin-containing monooxygenase</t>
+  </si>
+  <si>
+    <t>ABC transporter G family member</t>
+  </si>
+  <si>
+    <t>Nuclear transcription factor Y subunit B</t>
+  </si>
+  <si>
+    <t>gene_description</t>
   </si>
   <si>
     <r>
@@ -1920,1442 +3354,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">. List of leading-edge genes ranked by a combined score integrating GO-term contribution and expression change. </t>
+      <t xml:space="preserve">. List of putative core genes underlying GO term enrichment ranked by a combined score integrating GO term contribution and expression change. </t>
     </r>
-  </si>
-  <si>
-    <t>n = indicates the number of terms in which a gene appears.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_log2FC = is the mean log2 fold-change across pairwise contrasts, preserving direction of change. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_abs_log2FC = is the largest absolute log2 fold-change observed across contrasts. </t>
-  </si>
-  <si>
-    <t>score = combines term frequency and effect size (log1p(n) × max_abs_log2FC).</t>
-  </si>
-  <si>
-    <t>Apyrase</t>
-  </si>
-  <si>
-    <t>Metallothionein</t>
-  </si>
-  <si>
-    <t>S-adenosyl-L-methionine-dependent methyltransferases superfamily protein</t>
-  </si>
-  <si>
-    <t>Protein TIC 62, chloroplastic</t>
-  </si>
-  <si>
-    <t>Heat shock 70 kDa protein</t>
-  </si>
-  <si>
-    <t>Pheophorbide a oxygenase, chloroplastic</t>
-  </si>
-  <si>
-    <t>3-ketoacyl-CoA synthase</t>
-  </si>
-  <si>
-    <t>Monocopper oxidase-like protein SKU5</t>
-  </si>
-  <si>
-    <t>Phototropic-responsive NPH3 family protein</t>
-  </si>
-  <si>
-    <t>BTB/POZ domain-containing protein</t>
-  </si>
-  <si>
-    <t>Gamma-glutamyltranspeptidase family protein</t>
-  </si>
-  <si>
-    <t>RING/U-box superfamily protein, putative</t>
-  </si>
-  <si>
-    <t>Auxin influx transporter</t>
-  </si>
-  <si>
-    <t>WAT1-related protein</t>
-  </si>
-  <si>
-    <t>Basic blue protein</t>
-  </si>
-  <si>
-    <t>GDP-mannose transporter</t>
-  </si>
-  <si>
-    <t>MADS-box transcription factor</t>
-  </si>
-  <si>
-    <t>Transporter-related family protein</t>
-  </si>
-  <si>
-    <t>F-box family protein-like</t>
-  </si>
-  <si>
-    <t>Leucine-rich repeat protein kinase family protein</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol transfer protein Sec14p</t>
-  </si>
-  <si>
-    <t>Vacuolar sorting receptor family protein</t>
-  </si>
-  <si>
-    <t>Potassium channel</t>
-  </si>
-  <si>
-    <t>Auxin-responsive protein</t>
-  </si>
-  <si>
-    <t>Protein NRT1/ PTR FAMILY 2.3</t>
-  </si>
-  <si>
-    <t>Protein argonaute</t>
-  </si>
-  <si>
-    <t>Ethylene-responsive transcription factor</t>
-  </si>
-  <si>
-    <t>Purple acid phosphatase</t>
-  </si>
-  <si>
-    <t>Kinase, putative</t>
-  </si>
-  <si>
-    <t>MYB-related protein</t>
-  </si>
-  <si>
-    <t>Myb transcription factor</t>
-  </si>
-  <si>
-    <t>Bifunctional uridylyltransferase/uridylyl-removing enzyme</t>
-  </si>
-  <si>
-    <t>NAC domain protein</t>
-  </si>
-  <si>
-    <t>YABBY protein</t>
-  </si>
-  <si>
-    <t>Ras-related protein Rab-25</t>
-  </si>
-  <si>
-    <t>Molybdenum cofactor sulfurase</t>
-  </si>
-  <si>
-    <t>Sec14p-like phosphatidylinositol transfer family protein</t>
-  </si>
-  <si>
-    <t>Non-specific serine/threonine protein kinase</t>
-  </si>
-  <si>
-    <t>Target of rapamycin complex 2 subunit MAPKAP1</t>
-  </si>
-  <si>
-    <t>4-coumarate: CoA ligase</t>
-  </si>
-  <si>
-    <t>Calcium-dependent protein kinase</t>
-  </si>
-  <si>
-    <t>Glutamate receptor</t>
-  </si>
-  <si>
-    <t>Reticulon-like protein</t>
-  </si>
-  <si>
-    <t>Beta-xylosidase, putative</t>
-  </si>
-  <si>
-    <t>Adenylyl-sulfate kinase</t>
-  </si>
-  <si>
-    <t>Protein ZINC INDUCED FACILITATOR-LIKE 1</t>
-  </si>
-  <si>
-    <t>Alpha-L-arabinofuranosidase 1</t>
-  </si>
-  <si>
-    <t>Ras-related protein</t>
-  </si>
-  <si>
-    <t>Methylsterol monooxygenase 1-2</t>
-  </si>
-  <si>
-    <t>E3 ubiquitin-protein ligase</t>
-  </si>
-  <si>
-    <t>GATA transcription factor</t>
-  </si>
-  <si>
-    <t>NAC domain-containing protein</t>
-  </si>
-  <si>
-    <t>Protein kinase family protein, putative, expressed</t>
-  </si>
-  <si>
-    <t>RNA-directed DNA polymerase (reverse transcriptase)-related family protein</t>
-  </si>
-  <si>
-    <t>Trichome birefringence-like protein</t>
-  </si>
-  <si>
-    <t>L-ascorbate oxidase-like protein</t>
-  </si>
-  <si>
-    <t>ATP-dependent zinc metalloprotease FtsH 1</t>
-  </si>
-  <si>
-    <t>basic helix-loop-helix (bHLH) DNA-binding superfamily protein</t>
-  </si>
-  <si>
-    <t>Caleosin</t>
-  </si>
-  <si>
-    <t>Kinesin-like protein</t>
-  </si>
-  <si>
-    <t>Catalase</t>
-  </si>
-  <si>
-    <t>Raffinose synthase family protein</t>
-  </si>
-  <si>
-    <t>Phospholipid-transporting ATPase</t>
-  </si>
-  <si>
-    <t>Calcium sensing receptor, chloroplastic</t>
-  </si>
-  <si>
-    <t>BZIP transcription factor</t>
-  </si>
-  <si>
-    <t>Histidine kinase</t>
-  </si>
-  <si>
-    <t>MADS box transcription factor</t>
-  </si>
-  <si>
-    <t>NAC domain containing protein 82</t>
-  </si>
-  <si>
-    <t>Pleiotropic drug resistance ABC transporter</t>
-  </si>
-  <si>
-    <t>Glyceraldehyde-3-phosphate dehydrogenase</t>
-  </si>
-  <si>
-    <t>Alpha/beta-Hydrolases superfamily protein, putative</t>
-  </si>
-  <si>
-    <t>XH/XS domain-containing family protein</t>
-  </si>
-  <si>
-    <t>Kinase family protein</t>
-  </si>
-  <si>
-    <t>tRNA-modifying protein YgfZ</t>
-  </si>
-  <si>
-    <t>Cytochrome f</t>
-  </si>
-  <si>
-    <t>Chloride channel protein</t>
-  </si>
-  <si>
-    <t>MYB-related transcription factor</t>
-  </si>
-  <si>
-    <t>Cellulose synthase-like protein</t>
-  </si>
-  <si>
-    <t>Receptor protein kinase</t>
-  </si>
-  <si>
-    <t>AT hook motif DNA-binding family protein</t>
-  </si>
-  <si>
-    <t>transcription factor-like protein</t>
-  </si>
-  <si>
-    <t>Acidic endochitinase</t>
-  </si>
-  <si>
-    <t>Protein NRT1/ PTR FAMILY 1.2</t>
-  </si>
-  <si>
-    <t>Protein NRT1/ PTR FAMILY 1.1</t>
-  </si>
-  <si>
-    <t>Argonaute</t>
-  </si>
-  <si>
-    <t>Yellow stripe-like transporter 1</t>
-  </si>
-  <si>
-    <t>Protein ETHYLENE INSENSITIVE 3</t>
-  </si>
-  <si>
-    <t>BEL1-like homeodomain protein</t>
-  </si>
-  <si>
-    <t>Myosin family protein, putative, expressed</t>
-  </si>
-  <si>
-    <t>transmembrane protein</t>
-  </si>
-  <si>
-    <t>MYB transcription factor</t>
-  </si>
-  <si>
-    <t>Zinc-finger homeodomain protein 1</t>
-  </si>
-  <si>
-    <t>Nuclear transcription factor Y subunit</t>
-  </si>
-  <si>
-    <t>F5O11.10 isoform 1</t>
-  </si>
-  <si>
-    <t>TBC1 domain family member</t>
-  </si>
-  <si>
-    <t>Aspartic proteinase Asp1</t>
-  </si>
-  <si>
-    <t>MLO-like protein</t>
-  </si>
-  <si>
-    <t>Callose synthase-like protein</t>
-  </si>
-  <si>
-    <t>Phosphate translocator</t>
-  </si>
-  <si>
-    <t>Protein IQ-DOMAIN 1</t>
-  </si>
-  <si>
-    <t>Nodulin-like / Major Facilitator Superfamily protein</t>
-  </si>
-  <si>
-    <t>Heat shock transcription factor</t>
-  </si>
-  <si>
-    <t>Leucine-rich repeat receptor-like protein kinase</t>
-  </si>
-  <si>
-    <t>Protein DETOXIFICATION</t>
-  </si>
-  <si>
-    <t>Protodermal factor 1</t>
-  </si>
-  <si>
-    <t>Syntaxin, putative</t>
-  </si>
-  <si>
-    <t>ABC transporter B family protein</t>
-  </si>
-  <si>
-    <t>RAN GTPase activating protein 2</t>
-  </si>
-  <si>
-    <t>Receptor protein kinase, putative</t>
-  </si>
-  <si>
-    <t>Transcription factor</t>
-  </si>
-  <si>
-    <t>Protein lateral root primordium 1</t>
-  </si>
-  <si>
-    <t>Cytochrome b561 domain-containing protein</t>
-  </si>
-  <si>
-    <t>Heme oxygenase 1</t>
-  </si>
-  <si>
-    <t>Peptide transporter</t>
-  </si>
-  <si>
-    <t>Peroxidase</t>
-  </si>
-  <si>
-    <t>Two-component response regulator</t>
-  </si>
-  <si>
-    <t>Phosphoenolpyruvate carboxylase</t>
-  </si>
-  <si>
-    <t>Protein kinase family protein</t>
-  </si>
-  <si>
-    <t>Type I inositol-1,4,5-trisphosphate 5-phosphatase 1</t>
-  </si>
-  <si>
-    <t>O-acyltransferase</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol N-acetyglucosaminlytransferase subunit P-like protein</t>
-  </si>
-  <si>
-    <t>carboxyl-terminal peptidase, putative (DUF239)</t>
-  </si>
-  <si>
-    <t>Carboxypeptidase</t>
-  </si>
-  <si>
-    <t>Beta-fructofuranosidase, insoluble protein</t>
-  </si>
-  <si>
-    <t>Choline/ethanolamine kinase</t>
-  </si>
-  <si>
-    <t>Amino acid transporter-like protein</t>
-  </si>
-  <si>
-    <t>Zeaxanthin epoxidase, chloroplastic</t>
-  </si>
-  <si>
-    <t>ACT domain containing protein, expressed</t>
-  </si>
-  <si>
-    <t>Leucine-rich repeat receptor-like protein kinase family protein, putative</t>
-  </si>
-  <si>
-    <t>Leucine-rich repeat receptor-like protein kinase family protein</t>
-  </si>
-  <si>
-    <t>ABC subfamily C transporter</t>
-  </si>
-  <si>
-    <t>Zinc finger CCCH domain-containing protein 4</t>
-  </si>
-  <si>
-    <t>Ethylene-responsive transcription factor, putative</t>
-  </si>
-  <si>
-    <t>Xyloglucan galactosyltransferase KATAMARI1, putative</t>
-  </si>
-  <si>
-    <t>Sugar phosphate/phosphate translocator</t>
-  </si>
-  <si>
-    <t>Fructose-1,6-bisphosphatase class 1</t>
-  </si>
-  <si>
-    <t>Mitotic checkpoint protein bub3.1</t>
-  </si>
-  <si>
-    <t>Transport inhibitor response 1-like protein</t>
-  </si>
-  <si>
-    <t>Signal peptide peptidase family protein</t>
-  </si>
-  <si>
-    <t>Nucleosome assembly protein 1-like 1</t>
-  </si>
-  <si>
-    <t>Amino acid permease</t>
-  </si>
-  <si>
-    <t>Phospholipase A1</t>
-  </si>
-  <si>
-    <t>Glucan endo-1,3-beta-glucosidase, putative</t>
-  </si>
-  <si>
-    <t>Sugar transporter, putative</t>
-  </si>
-  <si>
-    <t>SPX domain-containing protein</t>
-  </si>
-  <si>
-    <t>Dof zinc finger protein</t>
-  </si>
-  <si>
-    <t>F-box protein</t>
-  </si>
-  <si>
-    <t>Phosphoinositide phospholipase C</t>
-  </si>
-  <si>
-    <t>Scarecrow transcription factor family protein</t>
-  </si>
-  <si>
-    <t>Chlorophyllide a oxygenase, chloroplastic</t>
-  </si>
-  <si>
-    <t>Amino acid permease family protein</t>
-  </si>
-  <si>
-    <t>Phenylalanine ammonia-lyase</t>
-  </si>
-  <si>
-    <t>Long-chain-fatty-acid CoA ligase, putative</t>
-  </si>
-  <si>
-    <t>DNA-binding protein SMUBP-2</t>
-  </si>
-  <si>
-    <t>Acetyl-coenzyme A synthetase</t>
-  </si>
-  <si>
-    <t>Germin-like protein 1</t>
-  </si>
-  <si>
-    <t>UPF0301 protein</t>
-  </si>
-  <si>
-    <t>2-phosphoglycerate kinase-related family protein</t>
-  </si>
-  <si>
-    <t>Protein PLASTID MOVEMENT IMPAIRED 2</t>
-  </si>
-  <si>
-    <t>Serine/Threonine-kinase WNK (WNK)-like protein</t>
-  </si>
-  <si>
-    <t>Glycerol kinase</t>
-  </si>
-  <si>
-    <t>Glutathione S-transferase</t>
-  </si>
-  <si>
-    <t>Calcium-dependent lipid-binding domain-containing protein</t>
-  </si>
-  <si>
-    <t>Glycosyltransferase</t>
-  </si>
-  <si>
-    <t>Glutamate decarboxylase</t>
-  </si>
-  <si>
-    <t>RING finger protein</t>
-  </si>
-  <si>
-    <t>CDT1-like protein a, chloroplastic</t>
-  </si>
-  <si>
-    <t>E3 ubiquitin-protein ligase RGLG2</t>
-  </si>
-  <si>
-    <t>Calcium-binding EF-hand family protein</t>
-  </si>
-  <si>
-    <t>Basic helix-loop-helix (BHLH) Transcription Factor</t>
-  </si>
-  <si>
-    <t>D-3-phosphoglycerate dehydrogenase</t>
-  </si>
-  <si>
-    <t>Receptor-like kinase</t>
-  </si>
-  <si>
-    <t>Orotate phosphoribosyltransferase, Orotidine-5'-phosphate decarboxylase</t>
-  </si>
-  <si>
-    <t>Proline transporter</t>
-  </si>
-  <si>
-    <t>ENTH/ANTH/VHS superfamily protein</t>
-  </si>
-  <si>
-    <t>U-box domain-containing protein</t>
-  </si>
-  <si>
-    <t>Endo-1,4-beta-xylanase, putative, expressed</t>
-  </si>
-  <si>
-    <t>Vesicle-associated 1-1-like protein</t>
-  </si>
-  <si>
-    <t>Chitinase-like protein</t>
-  </si>
-  <si>
-    <t>Calpain-like protein</t>
-  </si>
-  <si>
-    <t>Basic helix-loop-helix transcription factor</t>
-  </si>
-  <si>
-    <t>RING/U-box superfamily protein</t>
-  </si>
-  <si>
-    <t>Core-2/I-branching beta-1,6-N-acetylglucosaminyltransferase family protein</t>
-  </si>
-  <si>
-    <t>Receptor-like protein kinase</t>
-  </si>
-  <si>
-    <t>Lipase</t>
-  </si>
-  <si>
-    <t>LIGHT-DEPENDENT SHORT HYPOCOTYLS-like protein (DUF640)</t>
-  </si>
-  <si>
-    <t>Mitochondrial carrier protein, putative</t>
-  </si>
-  <si>
-    <t>TBC1 domain family member-like protein</t>
-  </si>
-  <si>
-    <t>Protein ABIL1</t>
-  </si>
-  <si>
-    <t>Fatty-acid desaturase</t>
-  </si>
-  <si>
-    <t>Glutamyl-tRNA reductase</t>
-  </si>
-  <si>
-    <t>Seipin</t>
-  </si>
-  <si>
-    <t>Pirin-like protein</t>
-  </si>
-  <si>
-    <t>Sphingoid base hydroxylase 2</t>
-  </si>
-  <si>
-    <t>Kinase-like protein</t>
-  </si>
-  <si>
-    <t>Basic helix loop helix (BHLH) family transcription factor</t>
-  </si>
-  <si>
-    <t>Subtilisin protease</t>
-  </si>
-  <si>
-    <t>Exocyst complex component, putative</t>
-  </si>
-  <si>
-    <t>WEB family protein, chloroplastic</t>
-  </si>
-  <si>
-    <t>Endo-1,3(4)-beta-glucanase 1</t>
-  </si>
-  <si>
-    <t>Aldose 1-epimerase-like</t>
-  </si>
-  <si>
-    <t>Tubby-like F-box protein</t>
-  </si>
-  <si>
-    <t>Regulator of chromosome condensation (RCC1) family with FYVE zinc finger domain-containing protein</t>
-  </si>
-  <si>
-    <t>Dicer-like protein 3</t>
-  </si>
-  <si>
-    <t>C2 calcium/lipid-binding and GRAM domain protein</t>
-  </si>
-  <si>
-    <t>Acetyl-CoA carboxylase</t>
-  </si>
-  <si>
-    <t>AGAMOUS MADS box factor transcription factor</t>
-  </si>
-  <si>
-    <t>glucan synthase-like 9</t>
-  </si>
-  <si>
-    <t>PPPDE thiol peptidase family protein, putative</t>
-  </si>
-  <si>
-    <t>Acetolactate synthase</t>
-  </si>
-  <si>
-    <t>AP2/B3 transcription factor family protein</t>
-  </si>
-  <si>
-    <t>Phosphate transporter</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol 3,4,5-trisphosphate 3-phosphatase and dual-specificity protein phosphatase PTEN</t>
-  </si>
-  <si>
-    <t>Zinc transporter</t>
-  </si>
-  <si>
-    <t>Metal transporter, putative</t>
-  </si>
-  <si>
-    <t>Pyruvate dehydrogenase E1 component alpha subunit</t>
-  </si>
-  <si>
-    <t>Nitrate transporter 1.1</t>
-  </si>
-  <si>
-    <t>Serine/threonine-protein phosphatase</t>
-  </si>
-  <si>
-    <t>Ribulose-phosphate 3-epimerase</t>
-  </si>
-  <si>
-    <t>transmembrane protein, putative (DUF679 domain membrane protein 2)</t>
-  </si>
-  <si>
-    <t>Calmodulin-binding transcription activator</t>
-  </si>
-  <si>
-    <t>Homeobox protein, putative</t>
-  </si>
-  <si>
-    <t>Transducin/WD40 repeat-like superfamily protein</t>
-  </si>
-  <si>
-    <t>Subtilisin-like protease</t>
-  </si>
-  <si>
-    <t>VQ motif family protein</t>
-  </si>
-  <si>
-    <t>CoA ligase</t>
-  </si>
-  <si>
-    <t>Guanylyl cyclase</t>
-  </si>
-  <si>
-    <t>Zinc finger-homeodomain protein 1</t>
-  </si>
-  <si>
-    <t>Protein strawberry notch-like protein 1</t>
-  </si>
-  <si>
-    <t>Protein DA1-related 1</t>
-  </si>
-  <si>
-    <t>LysM domain-containing GPI-anchored protein 1</t>
-  </si>
-  <si>
-    <t>Lactation elevated protein 1</t>
-  </si>
-  <si>
-    <t>Kelch repeat protein, putative</t>
-  </si>
-  <si>
-    <t>Aldo/keto reductase family-like protein</t>
-  </si>
-  <si>
-    <t>DNA polymerase delta small subunit</t>
-  </si>
-  <si>
-    <t>Leucine-rich repeat receptor-like kinase</t>
-  </si>
-  <si>
-    <t>Major facilitator superfamily transporter</t>
-  </si>
-  <si>
-    <t>Ring finger protein, putative</t>
-  </si>
-  <si>
-    <t>Methyltransferase</t>
-  </si>
-  <si>
-    <t>protein kinase family protein</t>
-  </si>
-  <si>
-    <t>E3 ubiquitin-protein ligase RGLG2-like protein</t>
-  </si>
-  <si>
-    <t>ABC transporter, putative</t>
-  </si>
-  <si>
-    <t>Malic enzyme</t>
-  </si>
-  <si>
-    <t>Calmodulin</t>
-  </si>
-  <si>
-    <t>Protein kinase</t>
-  </si>
-  <si>
-    <t>Ubiquitin-conjugating enzyme, E2</t>
-  </si>
-  <si>
-    <t>Ankyrin repeat protein-like</t>
-  </si>
-  <si>
-    <t>WEAK movement UNDER BLUE LIGHT-like protein</t>
-  </si>
-  <si>
-    <t>Mechanosensitive ion channel family protein</t>
-  </si>
-  <si>
-    <t>Synaptotagmin-5</t>
-  </si>
-  <si>
-    <t>ATP-dependent RNA helicase</t>
-  </si>
-  <si>
-    <t>Syntaxin</t>
-  </si>
-  <si>
-    <t>Pantothenate kinase family protein</t>
-  </si>
-  <si>
-    <t>Photosystem II reaction center PsbP family protein</t>
-  </si>
-  <si>
-    <t>Zinc finger (C3HC4-type RING finger) family protein</t>
-  </si>
-  <si>
-    <t>6-phosphogluconate dehydrogenase-like protein</t>
-  </si>
-  <si>
-    <t>Hexosyltransferase</t>
-  </si>
-  <si>
-    <t>C2 and GRAM domain-containing protein</t>
-  </si>
-  <si>
-    <t>Glycosyltransferases</t>
-  </si>
-  <si>
-    <t>Protein phosphatase 2C</t>
-  </si>
-  <si>
-    <t>Cryptochrome-1</t>
-  </si>
-  <si>
-    <t>Phosphoinositide phosphatase family protein</t>
-  </si>
-  <si>
-    <t>GATA transcription factor, putative</t>
-  </si>
-  <si>
-    <t>1,4-alpha-glucan branching enzyme GlgB</t>
-  </si>
-  <si>
-    <t>Glutamate synthase, putative</t>
-  </si>
-  <si>
-    <t>GPI inositol-deacylase</t>
-  </si>
-  <si>
-    <t>Glutathione-regulated potassium-efflux system protein</t>
-  </si>
-  <si>
-    <t>IQ domain-containing protein</t>
-  </si>
-  <si>
-    <t>Interactor of constitutive active ROPs 2, chloroplastic</t>
-  </si>
-  <si>
-    <t>Histone-lysine N-methyltransferase</t>
-  </si>
-  <si>
-    <t>CC-NBS-LRR family disease resistance protein</t>
-  </si>
-  <si>
-    <t>Xyloglucan alpha-1,6-xylosyltransferase</t>
-  </si>
-  <si>
-    <t>Ornithine decarboxylase</t>
-  </si>
-  <si>
-    <t>H/ACA ribonucleoprotein complex non-core subunit NAF1</t>
-  </si>
-  <si>
-    <t>Sucrose synthase</t>
-  </si>
-  <si>
-    <t>Calcium-transporting ATPase</t>
-  </si>
-  <si>
-    <t>Dolichol-phosphate mannosyltransferase, putative, expressed</t>
-  </si>
-  <si>
-    <t>UDP-glucose 4-epimerase, putative</t>
-  </si>
-  <si>
-    <t>Cytochrome P450, putative</t>
-  </si>
-  <si>
-    <t>Heparanase</t>
-  </si>
-  <si>
-    <t>Ankyrin repeat and BTB/POZ domain protein</t>
-  </si>
-  <si>
-    <t>Ankyrin repeat and BTB/POZ domain-containing protein 1</t>
-  </si>
-  <si>
-    <t>Vesicle-associated protein 1-1</t>
-  </si>
-  <si>
-    <t>Profilin</t>
-  </si>
-  <si>
-    <t>60S ribosomal export protein NMD3</t>
-  </si>
-  <si>
-    <t>Mitochondrial carrier family</t>
-  </si>
-  <si>
-    <t>GTP cyclohydrolase II/3,4-dihydroxy-2-butanone 4-phosphate synthase</t>
-  </si>
-  <si>
-    <t>Cyclin</t>
-  </si>
-  <si>
-    <t>Homeobox-leucine zipper family protein</t>
-  </si>
-  <si>
-    <t>RING/FYVE/PHD zinc finger superfamily protein</t>
-  </si>
-  <si>
-    <t>Carboxymethylenebutenolidase-like protein</t>
-  </si>
-  <si>
-    <t>TCP transcription factor</t>
-  </si>
-  <si>
-    <t>transcription repressor</t>
-  </si>
-  <si>
-    <t>Pumilio-like protein</t>
-  </si>
-  <si>
-    <t>Exocyst complex component EXO70A1</t>
-  </si>
-  <si>
-    <t>Argonaute family protein</t>
-  </si>
-  <si>
-    <t>Respiratory burst oxidase, putative</t>
-  </si>
-  <si>
-    <t>Homeobox protein BEL1-like protein</t>
-  </si>
-  <si>
-    <t>Cytochrome P450 family protein</t>
-  </si>
-  <si>
-    <t>2,3-bisphosphoglycerate-dependent phosphoglycerate mutase</t>
-  </si>
-  <si>
-    <t>RNA binding protein, putative</t>
-  </si>
-  <si>
-    <t>GEM-like protein 1</t>
-  </si>
-  <si>
-    <t>AT hook motif DNA-binding family protein, putative</t>
-  </si>
-  <si>
-    <t>Syntaxin protein</t>
-  </si>
-  <si>
-    <t>Leucine-rich repeat-containing protein</t>
-  </si>
-  <si>
-    <t>Mitochondrial carrier protein-like</t>
-  </si>
-  <si>
-    <t>Auxin efflux carrier family protein</t>
-  </si>
-  <si>
-    <t>Carotenoid isomerase, putative, expressed</t>
-  </si>
-  <si>
-    <t>Exostosin-2</t>
-  </si>
-  <si>
-    <t>Poly [ADP-ribose] polymerase</t>
-  </si>
-  <si>
-    <t>TBC1 domain family member 8B</t>
-  </si>
-  <si>
-    <t>DUF4228 domain protein</t>
-  </si>
-  <si>
-    <t>Coenzyme Q-binding protein COQ10, mitochondrial</t>
-  </si>
-  <si>
-    <t>Protein phosphatase 2c, putative</t>
-  </si>
-  <si>
-    <t>Acetyltransferase component of pyruvate dehydrogenase complex</t>
-  </si>
-  <si>
-    <t>Lorelei-like-GPI-anchored protein</t>
-  </si>
-  <si>
-    <t>DUF936 family protein</t>
-  </si>
-  <si>
-    <t>Respiratory burst oxidase homolog</t>
-  </si>
-  <si>
-    <t>Acyl-CoA-binding domain-containing protein 4</t>
-  </si>
-  <si>
-    <t>Presequence protease, mitochondrial</t>
-  </si>
-  <si>
-    <t>Alkaline/neutral invertase</t>
-  </si>
-  <si>
-    <t>Zinc finger protein</t>
-  </si>
-  <si>
-    <t>Jasmonate ZIM domain-containing protein</t>
-  </si>
-  <si>
-    <t>Receptor kinase</t>
-  </si>
-  <si>
-    <t>Endosomal targeting BRO1-like domain-containing protein</t>
-  </si>
-  <si>
-    <t>Dihydrolipoyl dehydrogenase</t>
-  </si>
-  <si>
-    <t>D-glycerate dehydrogenase/hydroxypyruvate reductase</t>
-  </si>
-  <si>
-    <t>Geranylgeranyl pyrophosphate synthase</t>
-  </si>
-  <si>
-    <t>Inositol-pentakisphosphate 2-kinase</t>
-  </si>
-  <si>
-    <t>Cytochrome b561 and DOMON domain-containing protein</t>
-  </si>
-  <si>
-    <t>Auxin response factor</t>
-  </si>
-  <si>
-    <t>BES1/BZR1 homolog 1</t>
-  </si>
-  <si>
-    <t>Chaperone protein dnaJ, putative</t>
-  </si>
-  <si>
-    <t>Alpha-glucosidase</t>
-  </si>
-  <si>
-    <t>Serine acetyltransferase</t>
-  </si>
-  <si>
-    <t>N-acetyltransferase, putative, expressed</t>
-  </si>
-  <si>
-    <t>Protein trichome birefringence</t>
-  </si>
-  <si>
-    <t>Sodium/hydrogen exchanger</t>
-  </si>
-  <si>
-    <t>Copper transporter family protein</t>
-  </si>
-  <si>
-    <t>Protein kinase 2A, chloroplastic</t>
-  </si>
-  <si>
-    <t>Eukaryotic aspartyl protease family protein</t>
-  </si>
-  <si>
-    <t>Phosphatidylcholine:diacylglycerol cholinephosphotransferase 1</t>
-  </si>
-  <si>
-    <t>Oxygen-dependent coproporphyrinogen-III oxidase</t>
-  </si>
-  <si>
-    <t>Programmed cell death-4</t>
-  </si>
-  <si>
-    <t>PsbP family protein, expressed</t>
-  </si>
-  <si>
-    <t>Protein kinase, putative</t>
-  </si>
-  <si>
-    <t>50S ribosomal protein L19, putative</t>
-  </si>
-  <si>
-    <t>ATP-dependent Clp protease ATP-binding subunit ClpB</t>
-  </si>
-  <si>
-    <t>Potassium efflux antiporter</t>
-  </si>
-  <si>
-    <t>Alpha/beta-Hydrolases superfamily protein</t>
-  </si>
-  <si>
-    <t>Terpene cyclase/mutase family member</t>
-  </si>
-  <si>
-    <t>WRKY transcription factor</t>
-  </si>
-  <si>
-    <t>Membrane protein of ER body-like protein</t>
-  </si>
-  <si>
-    <t>Membrane protein of er body-like protein</t>
-  </si>
-  <si>
-    <t>Cytochrome P450-like protein</t>
-  </si>
-  <si>
-    <t>Transcription elongation factor SPT5</t>
-  </si>
-  <si>
-    <t>Ubiquitin-conjugating enzyme E2</t>
-  </si>
-  <si>
-    <t>PAX-interacting protein 1</t>
-  </si>
-  <si>
-    <t>transmembrane protein, putative (DUF288)</t>
-  </si>
-  <si>
-    <t>Hedgehog-interacting-like protein</t>
-  </si>
-  <si>
-    <t>Citrate synthase</t>
-  </si>
-  <si>
-    <t>Cellulose synthase</t>
-  </si>
-  <si>
-    <t>Thymidine kinase</t>
-  </si>
-  <si>
-    <t>ORMDL family protein-like</t>
-  </si>
-  <si>
-    <t>Zinc finger SWIM domain-containing protein 7</t>
-  </si>
-  <si>
-    <t>Brevis radix-like protein</t>
-  </si>
-  <si>
-    <t>2-oxoglutarate (2OG) and Fe(II)-dependent oxygenase superfamily protein</t>
-  </si>
-  <si>
-    <t>FAD-binding Berberine family protein, putative</t>
-  </si>
-  <si>
-    <t>Resistance to phytophthora 1 protein</t>
-  </si>
-  <si>
-    <t>SPX domain-containing family protein</t>
-  </si>
-  <si>
-    <t>UDP-glucose pyrophosphorylase</t>
-  </si>
-  <si>
-    <t>Zinc finger CCCH domain protein</t>
-  </si>
-  <si>
-    <t>Uridylate kinase</t>
-  </si>
-  <si>
-    <t>Indole-3-acetic acid-amido synthetase GH3.3</t>
-  </si>
-  <si>
-    <t>Transcription factor, putative</t>
-  </si>
-  <si>
-    <t>Transporter</t>
-  </si>
-  <si>
-    <t>Gamma interferon inducible lysosomal thiol reductase family protein, expressed</t>
-  </si>
-  <si>
-    <t>Solanesyl diphosphate synthase family protein</t>
-  </si>
-  <si>
-    <t>Nudix hydrolase-like protein</t>
-  </si>
-  <si>
-    <t>Transaldolase</t>
-  </si>
-  <si>
-    <t>Serine/threonine protein phosphatase 2A regulatory subunit B</t>
-  </si>
-  <si>
-    <t>Glucose-1-phosphate adenylyltransferase</t>
-  </si>
-  <si>
-    <t>Leucine-rich repeat (LRR) family protein</t>
-  </si>
-  <si>
-    <t>Respiratory burst oxidase</t>
-  </si>
-  <si>
-    <t>Carbon catabolite repressor protein 4</t>
-  </si>
-  <si>
-    <t>Protein REVERSION-TO-ETHYLENE SENSITIVITY1</t>
-  </si>
-  <si>
-    <t>Acyl-CoA N-acyltransferase with RING/FYVE/PHD-type zinc finger protein</t>
-  </si>
-  <si>
-    <t>Trihelix transcription factor</t>
-  </si>
-  <si>
-    <t>F-box/kelch-repeat protein</t>
-  </si>
-  <si>
-    <t>DNA/RNA helicase protein</t>
-  </si>
-  <si>
-    <t>Acyl-CoA ligase-like</t>
-  </si>
-  <si>
-    <t>1-aminocyclopropane-1-carboxylate synthase</t>
-  </si>
-  <si>
-    <t>F-box-like protein</t>
-  </si>
-  <si>
-    <t>2-oxoglutarate-dependent dioxygenase</t>
-  </si>
-  <si>
-    <t>electron transporter, putative (Protein of unknown function, DUF547)</t>
-  </si>
-  <si>
-    <t>PI-PLC X domain-containing protein</t>
-  </si>
-  <si>
-    <t>Protein phosphatase 2C containing protein</t>
-  </si>
-  <si>
-    <t>Calcium dependent protein kinase</t>
-  </si>
-  <si>
-    <t>Cytokinin oxidase/dehydrogenase</t>
-  </si>
-  <si>
-    <t>Malonyl CoA-acyl carrier protein transacylase containing protein, expressed</t>
-  </si>
-  <si>
-    <t>BTB/POZ and MATH domain-containing protein 2</t>
-  </si>
-  <si>
-    <t>Aspartate aminotransferase</t>
-  </si>
-  <si>
-    <t>Glycerol-3-phosphate dehydrogenase [NAD(+)]</t>
-  </si>
-  <si>
-    <t>Vacuole membrane-like protein</t>
-  </si>
-  <si>
-    <t>Alpha-glucan water dikinase</t>
-  </si>
-  <si>
-    <t>Chorismate mutase</t>
-  </si>
-  <si>
-    <t>GRAM domain-containing protein / ABA-responsive</t>
-  </si>
-  <si>
-    <t>Beta-carotene hydroxylase, putative, expressed</t>
-  </si>
-  <si>
-    <t>ATP-dependent chaperone ClpB</t>
-  </si>
-  <si>
-    <t>F-box protein PP2-A13</t>
-  </si>
-  <si>
-    <t>UPF0496 protein</t>
-  </si>
-  <si>
-    <t>Mitochondrial carrier protein</t>
-  </si>
-  <si>
-    <t>Lysine-specific demethylase</t>
-  </si>
-  <si>
-    <t>Eukaryotic translation initiation factor 4G</t>
-  </si>
-  <si>
-    <t>Rho GTPase-activating protein</t>
-  </si>
-  <si>
-    <t>FAD binding protein</t>
-  </si>
-  <si>
-    <t>F-box family protein</t>
-  </si>
-  <si>
-    <t>TOX high mobility group box protein, putative (DUF1635)</t>
-  </si>
-  <si>
-    <t>Microtubule associated family protein</t>
-  </si>
-  <si>
-    <t>Tryptophan aminotransferase</t>
-  </si>
-  <si>
-    <t>Pyridoxamine 5-phosphate oxidase family protein</t>
-  </si>
-  <si>
-    <t>Translation initiation factor IF-2</t>
-  </si>
-  <si>
-    <t>Glutamate dehydrogenase</t>
-  </si>
-  <si>
-    <t>Calcineurin-like metallo-phosphoesterase superfamily</t>
-  </si>
-  <si>
-    <t>ARM repeat superfamily protein</t>
-  </si>
-  <si>
-    <t>Glucose-6-phosphate 1-dehydrogenase</t>
-  </si>
-  <si>
-    <t>ABC transporter ATP-binding protein</t>
-  </si>
-  <si>
-    <t>Mitochondrial import inner membrane translocase subunit Tim10 B</t>
-  </si>
-  <si>
-    <t>CAS1 domain-containing protein 1</t>
-  </si>
-  <si>
-    <t>Formin-like protein</t>
-  </si>
-  <si>
-    <t>Coiled-coil domain-containing 90B, mitochondrial</t>
-  </si>
-  <si>
-    <t>CRS2-associated factor 1, chloroplastic</t>
-  </si>
-  <si>
-    <t>Linalool synthase</t>
-  </si>
-  <si>
-    <t>Ferredoxin--NADP reductase</t>
-  </si>
-  <si>
-    <t>Kelch repeat-containing protein</t>
-  </si>
-  <si>
-    <t>Uridine kinase</t>
-  </si>
-  <si>
-    <t>Set1/Ash2 histone methyltransferase complex subunit ASH2</t>
-  </si>
-  <si>
-    <t>Carotenoid cleavage dioxygenase</t>
-  </si>
-  <si>
-    <t>Elongation factor 4</t>
-  </si>
-  <si>
-    <t>Glycogen synthase</t>
-  </si>
-  <si>
-    <t>Flap endonuclease 1</t>
-  </si>
-  <si>
-    <t>DNA mismatch repair protein mutS</t>
-  </si>
-  <si>
-    <t>GDT1-like protein</t>
-  </si>
-  <si>
-    <t>Mediator of RNA polymerase II transcription subunit 16</t>
-  </si>
-  <si>
-    <t>B3 domain-containing protein</t>
-  </si>
-  <si>
-    <t>RNA ligase/cyclic nucleotide phosphodiesterase family protein</t>
-  </si>
-  <si>
-    <t>Phosphoglycerate kinase</t>
-  </si>
-  <si>
-    <t>methyl esterase 12</t>
-  </si>
-  <si>
-    <t>Polyol transporter</t>
-  </si>
-  <si>
-    <t>ELMO domain containing protein</t>
-  </si>
-  <si>
-    <t>Tobamovirus multiplication protein</t>
-  </si>
-  <si>
-    <t>Dual specificity protein phosphatase family protein</t>
-  </si>
-  <si>
-    <t>Xyloglucan galactosyltransferase KATAMARI1-like protein</t>
-  </si>
-  <si>
-    <t>U-box domain-containing protein 4</t>
-  </si>
-  <si>
-    <t>Sphingosine-1-phosphate phosphatase 1</t>
-  </si>
-  <si>
-    <t>Dual specificity phosphatase family protein</t>
-  </si>
-  <si>
-    <t>Hsp70 nucleotide exchange factor fes1</t>
-  </si>
-  <si>
-    <t>Oxysterol-binding family protein</t>
-  </si>
-  <si>
-    <t>Protein SIP5</t>
-  </si>
-  <si>
-    <t>3-ketodihydrosphingosine reductase</t>
-  </si>
-  <si>
-    <t>3(2),5-bisphosphate nucleotidase HAL2</t>
-  </si>
-  <si>
-    <t>Chalcone--flavonone isomerase</t>
-  </si>
-  <si>
-    <t>Oxysterol-binding protein</t>
-  </si>
-  <si>
-    <t>4-alpha-glucanotransferase</t>
-  </si>
-  <si>
-    <t>ATP-dependent protease La (LON) domain-containing protein</t>
-  </si>
-  <si>
-    <t>High mobility group family protein</t>
-  </si>
-  <si>
-    <t>Flavonol synthase</t>
-  </si>
-  <si>
-    <t>Transporter family protein</t>
-  </si>
-  <si>
-    <t>TATA-binding protein associated factor-like protein</t>
-  </si>
-  <si>
-    <t>Ubiquinone biosynthesis O-methyltransferase</t>
-  </si>
-  <si>
-    <t>Flavin-containing monooxygenase</t>
-  </si>
-  <si>
-    <t>ABC transporter G family member</t>
-  </si>
-  <si>
-    <t>Nuclear transcription factor Y subunit B</t>
-  </si>
-  <si>
-    <t>gene_description</t>
   </si>
 </sst>
 </file>
@@ -3722,27 +3722,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>627</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -3782,7 +3782,7 @@
         <v>36.720586151965598</v>
       </c>
       <c r="F9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3802,7 +3802,7 @@
         <v>36.379908711123903</v>
       </c>
       <c r="F10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3822,7 +3822,7 @@
         <v>29.5983983257643</v>
       </c>
       <c r="F11" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -3842,7 +3842,7 @@
         <v>28.438218192652801</v>
       </c>
       <c r="F12" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -3862,7 +3862,7 @@
         <v>28.375686038828199</v>
       </c>
       <c r="F13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3882,7 +3882,7 @@
         <v>26.824168797592002</v>
       </c>
       <c r="F14" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3902,7 +3902,7 @@
         <v>26.672859528649301</v>
       </c>
       <c r="F15" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3922,7 +3922,7 @@
         <v>26.3838421817326</v>
       </c>
       <c r="F16" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -3942,7 +3942,7 @@
         <v>26.3346043152597</v>
       </c>
       <c r="F17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -3962,7 +3962,7 @@
         <v>25.8619426800967</v>
       </c>
       <c r="F18" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,7 +3982,7 @@
         <v>25.6532043140868</v>
       </c>
       <c r="F19" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -4002,7 +4002,7 @@
         <v>25.410464404096601</v>
       </c>
       <c r="F20" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -4022,7 +4022,7 @@
         <v>24.874491949335901</v>
       </c>
       <c r="F21" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -4042,7 +4042,7 @@
         <v>24.562965775436901</v>
       </c>
       <c r="F22" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -4062,7 +4062,7 @@
         <v>23.524574682404001</v>
       </c>
       <c r="F23" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -4082,7 +4082,7 @@
         <v>23.508204317912899</v>
       </c>
       <c r="F24" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -4102,7 +4102,7 @@
         <v>22.715238152920499</v>
       </c>
       <c r="F25" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -4122,7 +4122,7 @@
         <v>22.602334812785799</v>
       </c>
       <c r="F26" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -4142,7 +4142,7 @@
         <v>22.1259801597364</v>
       </c>
       <c r="F27" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -4162,7 +4162,7 @@
         <v>21.912102002231901</v>
       </c>
       <c r="F28" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -4182,7 +4182,7 @@
         <v>21.591462054176901</v>
       </c>
       <c r="F29" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -4202,7 +4202,7 @@
         <v>21.3960887635677</v>
       </c>
       <c r="F30" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -4222,7 +4222,7 @@
         <v>21.213238613634399</v>
       </c>
       <c r="F31" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -4242,7 +4242,7 @@
         <v>20.8429704254646</v>
       </c>
       <c r="F32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -4262,7 +4262,7 @@
         <v>20.640919027784602</v>
       </c>
       <c r="F33" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -4282,7 +4282,7 @@
         <v>20.589801479552701</v>
       </c>
       <c r="F34" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -4302,7 +4302,7 @@
         <v>20.5798125651948</v>
       </c>
       <c r="F35" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -4322,7 +4322,7 @@
         <v>20.476890899019899</v>
       </c>
       <c r="F36" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -4342,7 +4342,7 @@
         <v>20.212424633923501</v>
       </c>
       <c r="F37" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -4362,7 +4362,7 @@
         <v>19.955497586065</v>
       </c>
       <c r="F38" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -4382,7 +4382,7 @@
         <v>19.881848870695599</v>
       </c>
       <c r="F39" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -4402,7 +4402,7 @@
         <v>19.700276042991302</v>
       </c>
       <c r="F40" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -4422,7 +4422,7 @@
         <v>19.700276042991302</v>
       </c>
       <c r="F41" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -4442,7 +4442,7 @@
         <v>19.3189444642429</v>
       </c>
       <c r="F42" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -4462,7 +4462,7 @@
         <v>19.186215942509001</v>
       </c>
       <c r="F43" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -4482,7 +4482,7 @@
         <v>19.1118210459212</v>
       </c>
       <c r="F44" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -4502,7 +4502,7 @@
         <v>19.034001579737801</v>
       </c>
       <c r="F45" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -4522,7 +4522,7 @@
         <v>18.972975745334899</v>
       </c>
       <c r="F46" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -4542,7 +4542,7 @@
         <v>18.7892429586242</v>
       </c>
       <c r="F47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -4562,7 +4562,7 @@
         <v>18.781514475925299</v>
       </c>
       <c r="F48" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -4582,7 +4582,7 @@
         <v>18.672176029421099</v>
       </c>
       <c r="F49" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -4602,7 +4602,7 @@
         <v>18.316913942824701</v>
       </c>
       <c r="F50" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -4622,7 +4622,7 @@
         <v>18.045036063568499</v>
       </c>
       <c r="F51" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -4642,7 +4642,7 @@
         <v>18.003601628065098</v>
       </c>
       <c r="F52" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -4662,7 +4662,7 @@
         <v>17.996834816492001</v>
       </c>
       <c r="F53" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -4682,7 +4682,7 @@
         <v>17.862699659720199</v>
       </c>
       <c r="F54" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -4702,7 +4702,7 @@
         <v>17.451921974306401</v>
       </c>
       <c r="F55" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -4722,7 +4722,7 @@
         <v>17.381233492496602</v>
       </c>
       <c r="F56" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -4742,7 +4742,7 @@
         <v>17.233682282979402</v>
       </c>
       <c r="F57" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -4762,7 +4762,7 @@
         <v>17.083512077588701</v>
       </c>
       <c r="F58" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -4782,7 +4782,7 @@
         <v>17.0774530536669</v>
       </c>
       <c r="F59" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -4802,7 +4802,7 @@
         <v>16.778770144225501</v>
       </c>
       <c r="F60" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -4822,7 +4822,7 @@
         <v>16.7327476793524</v>
       </c>
       <c r="F61" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -4842,7 +4842,7 @@
         <v>16.7207420135354</v>
       </c>
       <c r="F62" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -4862,7 +4862,7 @@
         <v>16.578815769508299</v>
       </c>
       <c r="F63" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -4882,7 +4882,7 @@
         <v>16.450630835547901</v>
       </c>
       <c r="F64" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -4902,7 +4902,7 @@
         <v>16.4229116152902</v>
       </c>
       <c r="F65" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -4922,7 +4922,7 @@
         <v>16.1898167233302</v>
       </c>
       <c r="F66" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -4942,7 +4942,7 @@
         <v>16.0854693710126</v>
       </c>
       <c r="F67" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -4962,7 +4962,7 @@
         <v>16.040431538054701</v>
       </c>
       <c r="F68" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -4982,7 +4982,7 @@
         <v>15.9712084399298</v>
       </c>
       <c r="F69" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -5002,7 +5002,7 @@
         <v>15.919845878305001</v>
       </c>
       <c r="F70" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -5022,7 +5022,7 @@
         <v>15.774984955308801</v>
       </c>
       <c r="F71" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -5042,7 +5042,7 @@
         <v>15.669704066977999</v>
       </c>
       <c r="F72" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -5062,7 +5062,7 @@
         <v>15.3929304390788</v>
       </c>
       <c r="F73" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -5082,7 +5082,7 @@
         <v>15.3349839632184</v>
       </c>
       <c r="F74" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -5102,7 +5102,7 @@
         <v>15.2640902165759</v>
       </c>
       <c r="F75" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -5122,7 +5122,7 @@
         <v>15.168330523625199</v>
       </c>
       <c r="F76" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -5142,7 +5142,7 @@
         <v>15.1615973967172</v>
       </c>
       <c r="F77" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -5162,7 +5162,7 @@
         <v>15.1496831871191</v>
       </c>
       <c r="F78" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -5182,7 +5182,7 @@
         <v>15.1067311362913</v>
       </c>
       <c r="F79" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -5202,7 +5202,7 @@
         <v>14.996134084950199</v>
       </c>
       <c r="F80" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -5222,7 +5222,7 @@
         <v>14.842349660869401</v>
       </c>
       <c r="F81" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -5242,7 +5242,7 @@
         <v>14.7488932574734</v>
       </c>
       <c r="F82" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -5262,7 +5262,7 @@
         <v>14.583338956552399</v>
       </c>
       <c r="F83" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -5282,7 +5282,7 @@
         <v>14.408194254366601</v>
       </c>
       <c r="F84" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -5302,7 +5302,7 @@
         <v>14.3137827453408</v>
       </c>
       <c r="F85" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -5322,7 +5322,7 @@
         <v>14.2842036679885</v>
       </c>
       <c r="F86" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -5342,7 +5342,7 @@
         <v>14.174736943125501</v>
       </c>
       <c r="F87" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -5362,7 +5362,7 @@
         <v>14.0806334547267</v>
       </c>
       <c r="F88" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -5382,7 +5382,7 @@
         <v>13.9035058548712</v>
       </c>
       <c r="F89" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -5402,7 +5402,7 @@
         <v>13.8956381304464</v>
       </c>
       <c r="F90" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -5422,7 +5422,7 @@
         <v>13.8781104568586</v>
       </c>
       <c r="F91" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -5442,7 +5442,7 @@
         <v>13.605268960666701</v>
       </c>
       <c r="F92" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -5462,7 +5462,7 @@
         <v>13.485775805123099</v>
       </c>
       <c r="F93" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -5482,7 +5482,7 @@
         <v>13.469806295477699</v>
       </c>
       <c r="F94" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -5502,7 +5502,7 @@
         <v>13.3107928567999</v>
       </c>
       <c r="F95" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -5522,7 +5522,7 @@
         <v>13.2690287810385</v>
       </c>
       <c r="F96" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -5542,7 +5542,7 @@
         <v>13.2161967217259</v>
       </c>
       <c r="F97" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -5562,7 +5562,7 @@
         <v>13.2161967217259</v>
       </c>
       <c r="F98" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -5582,7 +5582,7 @@
         <v>13.2022898036047</v>
       </c>
       <c r="F99" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -5602,7 +5602,7 @@
         <v>13.180325774322499</v>
       </c>
       <c r="F100" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -5622,7 +5622,7 @@
         <v>13.157257709737401</v>
       </c>
       <c r="F101" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -5642,7 +5642,7 @@
         <v>12.7947541623793</v>
       </c>
       <c r="F102" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -5662,7 +5662,7 @@
         <v>12.7238109228685</v>
       </c>
       <c r="F103" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -5682,7 +5682,7 @@
         <v>12.6373785354898</v>
       </c>
       <c r="F104" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -5702,7 +5702,7 @@
         <v>12.6030973251583</v>
       </c>
       <c r="F105" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -5722,7 +5722,7 @@
         <v>12.600698114401601</v>
       </c>
       <c r="F106" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -5742,7 +5742,7 @@
         <v>12.5776386399719</v>
       </c>
       <c r="F107" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -5762,7 +5762,7 @@
         <v>12.5419768637166</v>
       </c>
       <c r="F108" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -5782,7 +5782,7 @@
         <v>12.176841620941</v>
       </c>
       <c r="F109" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -5802,7 +5802,7 @@
         <v>12.097181434883799</v>
       </c>
       <c r="F110" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -5822,7 +5822,7 @@
         <v>12.090615535130301</v>
       </c>
       <c r="F111" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -5842,7 +5842,7 @@
         <v>12.0716292793362</v>
       </c>
       <c r="F112" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -5862,7 +5862,7 @@
         <v>12.065254023216699</v>
       </c>
       <c r="F113" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -5882,7 +5882,7 @@
         <v>12.054814724247899</v>
       </c>
       <c r="F114" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -5902,7 +5902,7 @@
         <v>12.0136736297812</v>
       </c>
       <c r="F115" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -5922,7 +5922,7 @@
         <v>12.0135572938223</v>
       </c>
       <c r="F116" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -5942,7 +5942,7 @@
         <v>11.9990585498772</v>
       </c>
       <c r="F117" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -5962,7 +5962,7 @@
         <v>11.9584498634764</v>
       </c>
       <c r="F118" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -5982,7 +5982,7 @@
         <v>11.929929498639099</v>
       </c>
       <c r="F119" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -6002,7 +6002,7 @@
         <v>11.7845938678593</v>
       </c>
       <c r="F120" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -6022,7 +6022,7 @@
         <v>11.687971369425799</v>
       </c>
       <c r="F121" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -6042,7 +6042,7 @@
         <v>11.657863149336499</v>
       </c>
       <c r="F122" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -6062,7 +6062,7 @@
         <v>11.422342567243</v>
       </c>
       <c r="F123" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -6082,7 +6082,7 @@
         <v>11.3774220824378</v>
       </c>
       <c r="F124" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -6102,7 +6102,7 @@
         <v>11.3753937878983</v>
       </c>
       <c r="F125" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -6122,7 +6122,7 @@
         <v>11.3642884709231</v>
       </c>
       <c r="F126" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -6142,7 +6142,7 @@
         <v>11.3576296638368</v>
       </c>
       <c r="F127" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -6162,7 +6162,7 @@
         <v>11.326162251538801</v>
       </c>
       <c r="F128" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -6182,7 +6182,7 @@
         <v>11.3084382444728</v>
       </c>
       <c r="F129" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -6202,7 +6202,7 @@
         <v>11.307430597963</v>
       </c>
       <c r="F130" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -6222,7 +6222,7 @@
         <v>11.235835802725999</v>
       </c>
       <c r="F131" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -6242,7 +6242,7 @@
         <v>11.1712876004921</v>
       </c>
       <c r="F132" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -6262,7 +6262,7 @@
         <v>11.0855266899763</v>
       </c>
       <c r="F133" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -6282,7 +6282,7 @@
         <v>11.005066747310501</v>
       </c>
       <c r="F134" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
@@ -6302,7 +6302,7 @@
         <v>10.9861228866811</v>
       </c>
       <c r="F135" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -6322,7 +6322,7 @@
         <v>10.943453068981301</v>
       </c>
       <c r="F136" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -6342,7 +6342,7 @@
         <v>10.9267150863036</v>
       </c>
       <c r="F137" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -6362,7 +6362,7 @@
         <v>10.886439159538901</v>
       </c>
       <c r="F138" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -6382,7 +6382,7 @@
         <v>10.6980024374904</v>
       </c>
       <c r="F139" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
@@ -6402,7 +6402,7 @@
         <v>10.680748926062501</v>
       </c>
       <c r="F140" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -6422,7 +6422,7 @@
         <v>10.6466861094341</v>
       </c>
       <c r="F141" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -6442,7 +6442,7 @@
         <v>10.6394691309377</v>
       </c>
       <c r="F142" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -6462,7 +6462,7 @@
         <v>10.329914651485399</v>
       </c>
       <c r="F143" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -6482,7 +6482,7 @@
         <v>10.2495610755506</v>
       </c>
       <c r="F144" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -6502,7 +6502,7 @@
         <v>10.1887022585562</v>
       </c>
       <c r="F145" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -6522,7 +6522,7 @@
         <v>10.171636606858099</v>
       </c>
       <c r="F146" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -6542,7 +6542,7 @@
         <v>10.1397415906265</v>
       </c>
       <c r="F147" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -6562,7 +6562,7 @@
         <v>10.121486912939201</v>
       </c>
       <c r="F148" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -6582,7 +6582,7 @@
         <v>10.1002181292166</v>
       </c>
       <c r="F149" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -6602,7 +6602,7 @@
         <v>10.0532842647957</v>
       </c>
       <c r="F150" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
@@ -6622,7 +6622,7 @@
         <v>10.0507742314113</v>
       </c>
       <c r="F151" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -6642,7 +6642,7 @@
         <v>10.0431946505688</v>
       </c>
       <c r="F152" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -6662,7 +6662,7 @@
         <v>10.033362838030399</v>
       </c>
       <c r="F153" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -6682,7 +6682,7 @@
         <v>9.9913910633929692</v>
       </c>
       <c r="F154" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -6702,7 +6702,7 @@
         <v>9.9673328397798802</v>
       </c>
       <c r="F155" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -6722,7 +6722,7 @@
         <v>9.9543624178760908</v>
       </c>
       <c r="F156" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -6742,7 +6742,7 @@
         <v>9.9543624178760908</v>
       </c>
       <c r="F157" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -6762,7 +6762,7 @@
         <v>9.9473041601698995</v>
       </c>
       <c r="F158" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -6782,7 +6782,7 @@
         <v>9.9413619571784508</v>
       </c>
       <c r="F159" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -6802,7 +6802,7 @@
         <v>9.8861716933290005</v>
       </c>
       <c r="F160" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
@@ -6822,7 +6822,7 @@
         <v>9.8686014744254198</v>
       </c>
       <c r="F161" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -6842,7 +6842,7 @@
         <v>9.8212735108206601</v>
       </c>
       <c r="F162" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
@@ -6862,7 +6862,7 @@
         <v>9.8169191057824001</v>
       </c>
       <c r="F163" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -6882,7 +6882,7 @@
         <v>9.8073215976236394</v>
       </c>
       <c r="F164" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
@@ -6902,7 +6902,7 @@
         <v>9.7983727534201108</v>
       </c>
       <c r="F165" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
@@ -6922,7 +6922,7 @@
         <v>9.66095510707129</v>
       </c>
       <c r="F166" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
@@ -6942,7 +6942,7 @@
         <v>9.5974895117655308</v>
       </c>
       <c r="F167" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
@@ -6962,7 +6962,7 @@
         <v>9.5886043733806492</v>
       </c>
       <c r="F168" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -6982,7 +6982,7 @@
         <v>9.5793890223050298</v>
       </c>
       <c r="F169" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -7002,7 +7002,7 @@
         <v>9.5590578994879198</v>
       </c>
       <c r="F170" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -7022,7 +7022,7 @@
         <v>9.5260565412073408</v>
       </c>
       <c r="F171" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
@@ -7042,7 +7042,7 @@
         <v>9.4828238730646603</v>
       </c>
       <c r="F172" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
@@ -7062,7 +7062,7 @@
         <v>9.4441278749191806</v>
       </c>
       <c r="F173" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
@@ -7082,7 +7082,7 @@
         <v>9.41700809744437</v>
       </c>
       <c r="F174" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
@@ -7102,7 +7102,7 @@
         <v>9.3903424102422104</v>
       </c>
       <c r="F175" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -7122,7 +7122,7 @@
         <v>9.3435913542858504</v>
       </c>
       <c r="F176" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
@@ -7142,7 +7142,7 @@
         <v>9.1851843700952305</v>
       </c>
       <c r="F177" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
@@ -7162,7 +7162,7 @@
         <v>9.1726597867806596</v>
       </c>
       <c r="F178" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
@@ -7182,7 +7182,7 @@
         <v>9.1475520436454794</v>
       </c>
       <c r="F179" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
@@ -7202,7 +7202,7 @@
         <v>9.1445877796804496</v>
       </c>
       <c r="F180" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -7222,7 +7222,7 @@
         <v>9.0792286726436604</v>
       </c>
       <c r="F181" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -7242,7 +7242,7 @@
         <v>9.0760000746737504</v>
       </c>
       <c r="F182" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
@@ -7262,7 +7262,7 @@
         <v>9.0663130946488995</v>
       </c>
       <c r="F183" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -7282,7 +7282,7 @@
         <v>8.9970082393929705</v>
       </c>
       <c r="F184" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
@@ -7302,7 +7302,7 @@
         <v>8.9630454366620391</v>
       </c>
       <c r="F185" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
@@ -7322,7 +7322,7 @@
         <v>8.8167104919219099</v>
       </c>
       <c r="F186" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
@@ -7342,7 +7342,7 @@
         <v>8.8068693697684406</v>
       </c>
       <c r="F187" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -7362,7 +7362,7 @@
         <v>8.8024451201718499</v>
       </c>
       <c r="F188" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
@@ -7382,7 +7382,7 @@
         <v>8.7857511864081701</v>
       </c>
       <c r="F189" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
@@ -7402,7 +7402,7 @@
         <v>8.7397574496245198</v>
       </c>
       <c r="F190" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
@@ -7422,7 +7422,7 @@
         <v>8.7333862483311808</v>
       </c>
       <c r="F191" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -7442,7 +7442,7 @@
         <v>8.6149297898807493</v>
       </c>
       <c r="F192" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
@@ -7462,7 +7462,7 @@
         <v>8.5845820665692791</v>
       </c>
       <c r="F193" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
@@ -7482,7 +7482,7 @@
         <v>8.4523158130940406</v>
       </c>
       <c r="F194" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
@@ -7502,7 +7502,7 @@
         <v>8.3521054416417204</v>
       </c>
       <c r="F195" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
@@ -7522,7 +7522,7 @@
         <v>8.3473117665259409</v>
       </c>
       <c r="F196" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
@@ -7542,7 +7542,7 @@
         <v>8.3355703732787898</v>
       </c>
       <c r="F197" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -7562,7 +7562,7 @@
         <v>8.3231770025585092</v>
       </c>
       <c r="F198" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -7582,7 +7582,7 @@
         <v>8.3127520369808003</v>
       </c>
       <c r="F199" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -7602,7 +7602,7 @@
         <v>8.2894415390943408</v>
       </c>
       <c r="F200" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
@@ -7622,7 +7622,7 @@
         <v>8.2503311048861807</v>
       </c>
       <c r="F201" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
@@ -7642,7 +7642,7 @@
         <v>8.2350191175959306</v>
       </c>
       <c r="F202" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
@@ -7662,7 +7662,7 @@
         <v>8.1610315376768892</v>
       </c>
       <c r="F203" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
@@ -7682,7 +7682,7 @@
         <v>8.1018793971675205</v>
       </c>
       <c r="F204" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
@@ -7702,7 +7702,7 @@
         <v>8.0943047112455595</v>
       </c>
       <c r="F205" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
@@ -7722,7 +7722,7 @@
         <v>8.0377423719630503</v>
       </c>
       <c r="F206" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
@@ -7742,7 +7742,7 @@
         <v>7.9852012188942902</v>
       </c>
       <c r="F207" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
@@ -7762,7 +7762,7 @@
         <v>7.9618273718585701</v>
       </c>
       <c r="F208" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
@@ -7782,7 +7782,7 @@
         <v>7.9369849980118801</v>
       </c>
       <c r="F209" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
@@ -7802,7 +7802,7 @@
         <v>7.8766041181646198</v>
       </c>
       <c r="F210" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -7822,7 +7822,7 @@
         <v>7.8483555755187897</v>
       </c>
       <c r="F211" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
@@ -7842,7 +7842,7 @@
         <v>7.8437287598413397</v>
       </c>
       <c r="F212" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
@@ -7862,7 +7862,7 @@
         <v>7.8105371765875402</v>
       </c>
       <c r="F213" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
@@ -7882,7 +7882,7 @@
         <v>7.6893367115066198</v>
       </c>
       <c r="F214" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
@@ -7902,7 +7902,7 @@
         <v>7.6231234903635299</v>
       </c>
       <c r="F215" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
@@ -7922,7 +7922,7 @@
         <v>7.6180113138899399</v>
       </c>
       <c r="F216" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -7942,7 +7942,7 @@
         <v>7.5748012258119202</v>
       </c>
       <c r="F217" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -7962,7 +7962,7 @@
         <v>7.5660987936497301</v>
       </c>
       <c r="F218" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
@@ -7982,7 +7982,7 @@
         <v>7.5069339142187497</v>
       </c>
       <c r="F219" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -8002,7 +8002,7 @@
         <v>7.4823473585593101</v>
       </c>
       <c r="F220" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
@@ -8022,7 +8022,7 @@
         <v>7.4468809564923903</v>
       </c>
       <c r="F221" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
@@ -8042,7 +8042,7 @@
         <v>7.4320162430043801</v>
       </c>
       <c r="F222" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
@@ -8062,7 +8062,7 @@
         <v>7.4186898722095398</v>
       </c>
       <c r="F223" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -8082,7 +8082,7 @@
         <v>7.4089673934201796</v>
       </c>
       <c r="F224" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
@@ -8102,7 +8102,7 @@
         <v>7.3885723671691004</v>
       </c>
       <c r="F225" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
@@ -8122,7 +8122,7 @@
         <v>7.3692065703513698</v>
       </c>
       <c r="F226" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -8142,7 +8142,7 @@
         <v>7.3658458416664896</v>
       </c>
       <c r="F227" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
@@ -8162,7 +8162,7 @@
         <v>7.3270197326630599</v>
       </c>
       <c r="F228" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -8182,7 +8182,7 @@
         <v>7.3028646551154397</v>
       </c>
       <c r="F229" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
@@ -8202,7 +8202,7 @@
         <v>7.2847176028708001</v>
       </c>
       <c r="F230" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
@@ -8222,7 +8222,7 @@
         <v>7.24043443158501</v>
       </c>
       <c r="F231" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
@@ -8242,7 +8242,7 @@
         <v>7.2287244658529399</v>
       </c>
       <c r="F232" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
@@ -8262,7 +8262,7 @@
         <v>7.1479993165243396</v>
       </c>
       <c r="F233" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
@@ -8282,7 +8282,7 @@
         <v>7.1433648992877998</v>
       </c>
       <c r="F234" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
@@ -8302,7 +8302,7 @@
         <v>7.1432020374203997</v>
       </c>
       <c r="F235" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
@@ -8322,7 +8322,7 @@
         <v>7.1426732683160203</v>
       </c>
       <c r="F236" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
@@ -8342,7 +8342,7 @@
         <v>7.1319138084263001</v>
       </c>
       <c r="F237" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -8362,7 +8362,7 @@
         <v>7.0912214343747104</v>
       </c>
       <c r="F238" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
@@ -8382,7 +8382,7 @@
         <v>7.0740916250729304</v>
       </c>
       <c r="F239" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -8402,7 +8402,7 @@
         <v>7.06576664497506</v>
       </c>
       <c r="F240" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
@@ -8422,7 +8422,7 @@
         <v>7.05992985303285</v>
       </c>
       <c r="F241" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -8442,7 +8442,7 @@
         <v>7.0273530973057197</v>
       </c>
       <c r="F242" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
@@ -8462,7 +8462,7 @@
         <v>7.0189076386007301</v>
       </c>
       <c r="F243" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -8482,7 +8482,7 @@
         <v>6.99641921803999</v>
       </c>
       <c r="F244" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
@@ -8502,7 +8502,7 @@
         <v>6.9800455751615802</v>
       </c>
       <c r="F245" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
@@ -8522,7 +8522,7 @@
         <v>6.9601098820038203</v>
       </c>
       <c r="F246" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
@@ -8542,7 +8542,7 @@
         <v>6.90313828297153</v>
       </c>
       <c r="F247" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
@@ -8562,7 +8562,7 @@
         <v>6.8955198025533804</v>
       </c>
       <c r="F248" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
@@ -8582,7 +8582,7 @@
         <v>6.8668171266808598</v>
       </c>
       <c r="F249" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
@@ -8602,7 +8602,7 @@
         <v>6.8611349887950404</v>
       </c>
       <c r="F250" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -8622,7 +8622,7 @@
         <v>6.7729338967289898</v>
       </c>
       <c r="F251" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -8642,7 +8642,7 @@
         <v>6.7412351703686904</v>
       </c>
       <c r="F252" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
@@ -8662,7 +8662,7 @@
         <v>6.73621946206669</v>
       </c>
       <c r="F253" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -8682,7 +8682,7 @@
         <v>6.7357034970143603</v>
       </c>
       <c r="F254" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
@@ -8702,7 +8702,7 @@
         <v>6.7178791381880103</v>
       </c>
       <c r="F255" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
@@ -8722,7 +8722,7 @@
         <v>6.6760545769181698</v>
       </c>
       <c r="F256" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -8742,7 +8742,7 @@
         <v>6.5785176623739003</v>
       </c>
       <c r="F257" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
@@ -8762,7 +8762,7 @@
         <v>6.5585300291896296</v>
       </c>
       <c r="F258" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -8782,7 +8782,7 @@
         <v>6.5583048679177596</v>
       </c>
       <c r="F259" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
@@ -8802,7 +8802,7 @@
         <v>6.5081300923088197</v>
       </c>
       <c r="F260" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
@@ -8822,7 +8822,7 @@
         <v>6.5064477687446001</v>
       </c>
       <c r="F261" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -8842,7 +8842,7 @@
         <v>6.4993587560083999</v>
       </c>
       <c r="F262" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
@@ -8862,7 +8862,7 @@
         <v>6.47817539348328</v>
       </c>
       <c r="F263" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -8882,7 +8882,7 @@
         <v>6.4764001953892096</v>
       </c>
       <c r="F264" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
@@ -8902,7 +8902,7 @@
         <v>6.4201984904888096</v>
       </c>
       <c r="F265" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
@@ -8922,7 +8922,7 @@
         <v>6.36922147210145</v>
       </c>
       <c r="F266" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
@@ -8942,7 +8942,7 @@
         <v>6.3120473188455097</v>
       </c>
       <c r="F267" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
@@ -8962,7 +8962,7 @@
         <v>6.3007617447694804</v>
       </c>
       <c r="F268" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
@@ -8982,7 +8982,7 @@
         <v>6.2900903590650197</v>
       </c>
       <c r="F269" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
@@ -9002,7 +9002,7 @@
         <v>6.1967465935866599</v>
       </c>
       <c r="F270" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
@@ -9022,7 +9022,7 @@
         <v>6.1936444177675796</v>
       </c>
       <c r="F271" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
@@ -9042,7 +9042,7 @@
         <v>6.1304401057199902</v>
       </c>
       <c r="F272" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
@@ -9062,7 +9062,7 @@
         <v>6.09200180082677</v>
       </c>
       <c r="F273" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
@@ -9082,7 +9082,7 @@
         <v>6.0683833041123902</v>
       </c>
       <c r="F274" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
@@ -9102,7 +9102,7 @@
         <v>6.0408497722887304</v>
       </c>
       <c r="F275" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
@@ -9122,7 +9122,7 @@
         <v>6.0202191297093099</v>
       </c>
       <c r="F276" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
@@ -9142,7 +9142,7 @@
         <v>5.9977986653781601</v>
       </c>
       <c r="F277" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
@@ -9162,7 +9162,7 @@
         <v>5.9556279750532299</v>
       </c>
       <c r="F278" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
@@ -9182,7 +9182,7 @@
         <v>5.9415869721297199</v>
       </c>
       <c r="F279" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
@@ -9202,7 +9202,7 @@
         <v>5.9360999156349097</v>
       </c>
       <c r="F280" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
@@ -9222,7 +9222,7 @@
         <v>5.9338256731312402</v>
       </c>
       <c r="F281" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
@@ -9242,7 +9242,7 @@
         <v>5.8744284196955903</v>
       </c>
       <c r="F282" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
@@ -9262,7 +9262,7 @@
         <v>5.8540220718590303</v>
       </c>
       <c r="F283" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
@@ -9282,7 +9282,7 @@
         <v>5.8521310480324296</v>
       </c>
       <c r="F284" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
@@ -9302,7 +9302,7 @@
         <v>5.8356887568300202</v>
       </c>
       <c r="F285" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
@@ -9322,7 +9322,7 @@
         <v>5.7953837460932602</v>
       </c>
       <c r="F286" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
@@ -9342,7 +9342,7 @@
         <v>5.7863034924084404</v>
       </c>
       <c r="F287" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
@@ -9362,7 +9362,7 @@
         <v>5.7665958313698003</v>
       </c>
       <c r="F288" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
@@ -9382,7 +9382,7 @@
         <v>5.76096268141122</v>
       </c>
       <c r="F289" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
@@ -9402,7 +9402,7 @@
         <v>5.7607246343219103</v>
       </c>
       <c r="F290" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
@@ -9422,7 +9422,7 @@
         <v>5.7505684589115198</v>
       </c>
       <c r="F291" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
@@ -9442,7 +9442,7 @@
         <v>5.7457961924135299</v>
       </c>
       <c r="F292" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
@@ -9462,7 +9462,7 @@
         <v>5.7194624376541201</v>
       </c>
       <c r="F293" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
@@ -9482,7 +9482,7 @@
         <v>5.71146086730724</v>
       </c>
       <c r="F294" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
@@ -9502,7 +9502,7 @@
         <v>5.6868655717945797</v>
       </c>
       <c r="F295" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
@@ -9522,7 +9522,7 @@
         <v>5.6799193140006201</v>
       </c>
       <c r="F296" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
@@ -9542,7 +9542,7 @@
         <v>5.6570591539654496</v>
       </c>
       <c r="F297" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
@@ -9562,7 +9562,7 @@
         <v>5.6507034655084203</v>
       </c>
       <c r="F298" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
@@ -9582,7 +9582,7 @@
         <v>5.6487388531276297</v>
       </c>
       <c r="F299" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
@@ -9602,7 +9602,7 @@
         <v>5.6465499028300803</v>
       </c>
       <c r="F300" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
@@ -9622,7 +9622,7 @@
         <v>5.6355986161057601</v>
       </c>
       <c r="F301" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
@@ -9642,7 +9642,7 @@
         <v>5.6188647299897498</v>
       </c>
       <c r="F302" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
@@ -9662,7 +9662,7 @@
         <v>5.5978934567913203</v>
       </c>
       <c r="F303" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
@@ -9682,7 +9682,7 @@
         <v>5.5683366094942999</v>
       </c>
       <c r="F304" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
@@ -9702,7 +9702,7 @@
         <v>5.5531164822496502</v>
       </c>
       <c r="F305" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
@@ -9722,7 +9722,7 @@
         <v>5.5357487934304803</v>
       </c>
       <c r="F306" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
@@ -9742,7 +9742,7 @@
         <v>5.4990848719096697</v>
       </c>
       <c r="F307" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
@@ -9762,7 +9762,7 @@
         <v>5.44948807291438</v>
       </c>
       <c r="F308" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
@@ -9782,7 +9782,7 @@
         <v>5.4476747989646297</v>
       </c>
       <c r="F309" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
@@ -9802,7 +9802,7 @@
         <v>5.3962552353462199</v>
       </c>
       <c r="F310" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
@@ -9822,7 +9822,7 @@
         <v>5.3700176378374103</v>
       </c>
       <c r="F311" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
@@ -9842,7 +9842,7 @@
         <v>5.3677999735550399</v>
       </c>
       <c r="F312" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
@@ -9862,7 +9862,7 @@
         <v>5.3656149852126296</v>
       </c>
       <c r="F313" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
@@ -9882,7 +9882,7 @@
         <v>5.3499190005509902</v>
       </c>
       <c r="F314" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
@@ -9902,7 +9902,7 @@
         <v>5.3272773836448399</v>
       </c>
       <c r="F315" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
@@ -9922,7 +9922,7 @@
         <v>5.3192601869810199</v>
       </c>
       <c r="F316" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
@@ -9942,7 +9942,7 @@
         <v>5.2891308896034204</v>
       </c>
       <c r="F317" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
@@ -9962,7 +9962,7 @@
         <v>5.2508709334376196</v>
       </c>
       <c r="F318" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
@@ -9982,7 +9982,7 @@
         <v>5.2400518036661303</v>
       </c>
       <c r="F319" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
@@ -10002,7 +10002,7 @@
         <v>5.2261454319473204</v>
       </c>
       <c r="F320" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
@@ -10022,7 +10022,7 @@
         <v>5.1988570420955504</v>
       </c>
       <c r="F321" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
@@ -10042,7 +10042,7 @@
         <v>5.0801979900216798</v>
       </c>
       <c r="F322" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
@@ -10062,7 +10062,7 @@
         <v>5.0533432003168999</v>
       </c>
       <c r="F323" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
@@ -10082,7 +10082,7 @@
         <v>5.0518841987690699</v>
       </c>
       <c r="F324" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
@@ -10102,7 +10102,7 @@
         <v>4.9803930802488496</v>
       </c>
       <c r="F325" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
@@ -10122,7 +10122,7 @@
         <v>4.9469140340737399</v>
       </c>
       <c r="F326" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
@@ -10142,7 +10142,7 @@
         <v>4.9395370747425504</v>
       </c>
       <c r="F327" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
@@ -10162,7 +10162,7 @@
         <v>4.9363261204278297</v>
       </c>
       <c r="F328" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
@@ -10182,7 +10182,7 @@
         <v>4.8752779203898102</v>
       </c>
       <c r="F329" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
@@ -10202,7 +10202,7 @@
         <v>4.8489222301028203</v>
       </c>
       <c r="F330" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
@@ -10222,7 +10222,7 @@
         <v>4.8108119852551203</v>
       </c>
       <c r="F331" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
@@ -10242,7 +10242,7 @@
         <v>4.7780583698138299</v>
       </c>
       <c r="F332" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
@@ -10262,7 +10262,7 @@
         <v>4.7551946726561001</v>
       </c>
       <c r="F333" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
@@ -10282,7 +10282,7 @@
         <v>4.7487227226827997</v>
       </c>
       <c r="F334" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
@@ -10302,7 +10302,7 @@
         <v>4.7416980164540501</v>
       </c>
       <c r="F335" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
@@ -10322,7 +10322,7 @@
         <v>4.7321939103357504</v>
       </c>
       <c r="F336" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
@@ -10342,7 +10342,7 @@
         <v>4.71553653889399</v>
       </c>
       <c r="F337" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
@@ -10362,7 +10362,7 @@
         <v>4.6897225279282502</v>
       </c>
       <c r="F338" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
@@ -10382,7 +10382,7 @@
         <v>4.6589850918279403</v>
       </c>
       <c r="F339" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
@@ -10402,7 +10402,7 @@
         <v>4.6324796551989103</v>
       </c>
       <c r="F340" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
@@ -10422,7 +10422,7 @@
         <v>4.6281634939169596</v>
       </c>
       <c r="F341" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
@@ -10442,7 +10442,7 @@
         <v>4.6248849506470897</v>
       </c>
       <c r="F342" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
@@ -10462,7 +10462,7 @@
         <v>4.6241056690485696</v>
       </c>
       <c r="F343" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
@@ -10482,7 +10482,7 @@
         <v>4.5811308494089102</v>
       </c>
       <c r="F344" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
@@ -10502,7 +10502,7 @@
         <v>4.5635639307285603</v>
       </c>
       <c r="F345" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
@@ -10522,7 +10522,7 @@
         <v>4.5375851846233699</v>
       </c>
       <c r="F346" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
@@ -10542,7 +10542,7 @@
         <v>4.5017060801405302</v>
       </c>
       <c r="F347" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
@@ -10562,7 +10562,7 @@
         <v>4.4924297549207104</v>
       </c>
       <c r="F348" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
@@ -10582,7 +10582,7 @@
         <v>4.4683218881485498</v>
       </c>
       <c r="F349" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
@@ -10602,7 +10602,7 @@
         <v>4.4460445451803698</v>
       </c>
       <c r="F350" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
@@ -10622,7 +10622,7 @@
         <v>4.4087349296972</v>
       </c>
       <c r="F351" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
@@ -10642,7 +10642,7 @@
         <v>4.3396995207840598</v>
       </c>
       <c r="F352" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
@@ -10662,7 +10662,7 @@
         <v>4.3362837612531901</v>
       </c>
       <c r="F353" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
@@ -10682,7 +10682,7 @@
         <v>4.3323417960261503</v>
       </c>
       <c r="F354" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
@@ -10702,7 +10702,7 @@
         <v>4.3304738036856403</v>
       </c>
       <c r="F355" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
@@ -10722,7 +10722,7 @@
         <v>4.3254613188698698</v>
       </c>
       <c r="F356" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
@@ -10742,7 +10742,7 @@
         <v>4.3254613188698698</v>
       </c>
       <c r="F357" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
@@ -10762,7 +10762,7 @@
         <v>4.3224101657762501</v>
       </c>
       <c r="F358" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
@@ -10782,7 +10782,7 @@
         <v>4.3207566079005097</v>
       </c>
       <c r="F359" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.3">
@@ -10802,7 +10802,7 @@
         <v>4.2967801475052498</v>
       </c>
       <c r="F360" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
@@ -10822,7 +10822,7 @@
         <v>4.2840709705767299</v>
       </c>
       <c r="F361" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.3">
@@ -10842,7 +10842,7 @@
         <v>4.1976799337289803</v>
       </c>
       <c r="F362" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.3">
@@ -10862,7 +10862,7 @@
         <v>4.1706732469325498</v>
       </c>
       <c r="F363" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
@@ -10882,7 +10882,7 @@
         <v>4.1617012843110501</v>
       </c>
       <c r="F364" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
@@ -10902,7 +10902,7 @@
         <v>4.1559519644161904</v>
       </c>
       <c r="F365" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
@@ -10922,7 +10922,7 @@
         <v>4.1475840662413299</v>
       </c>
       <c r="F366" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
@@ -10942,7 +10942,7 @@
         <v>4.1324963281864804</v>
       </c>
       <c r="F367" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
@@ -10962,7 +10962,7 @@
         <v>4.1163291783837996</v>
       </c>
       <c r="F368" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
@@ -10982,7 +10982,7 @@
         <v>4.09390160729874</v>
       </c>
       <c r="F369" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
@@ -11002,7 +11002,7 @@
         <v>4.0636369884159302</v>
       </c>
       <c r="F370" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
@@ -11022,7 +11022,7 @@
         <v>4.0343984656052303</v>
       </c>
       <c r="F371" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
@@ -11042,7 +11042,7 @@
         <v>4.02819348258374</v>
       </c>
       <c r="F372" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
@@ -11062,7 +11062,7 @@
         <v>3.9945162741770801</v>
       </c>
       <c r="F373" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
@@ -11082,7 +11082,7 @@
         <v>3.9730955895742799</v>
       </c>
       <c r="F374" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
@@ -11102,7 +11102,7 @@
         <v>3.9318256327243302</v>
       </c>
       <c r="F375" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
@@ -11122,7 +11122,7 @@
         <v>3.9121250410386601</v>
       </c>
       <c r="F376" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.3">
@@ -11142,7 +11142,7 @@
         <v>3.90080213621121</v>
       </c>
       <c r="F377" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
@@ -11162,7 +11162,7 @@
         <v>3.81889788850359</v>
       </c>
       <c r="F378" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
@@ -11182,7 +11182,7 @@
         <v>3.8063155397104902</v>
       </c>
       <c r="F379" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.3">
@@ -11202,7 +11202,7 @@
         <v>3.78266526676145</v>
       </c>
       <c r="F380" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
@@ -11222,7 +11222,7 @@
         <v>3.7749925564429301</v>
       </c>
       <c r="F381" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
@@ -11242,7 +11242,7 @@
         <v>3.7727609380946401</v>
       </c>
       <c r="F382" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
@@ -11262,7 +11262,7 @@
         <v>3.7603189083458801</v>
       </c>
       <c r="F383" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
@@ -11282,7 +11282,7 @@
         <v>3.74360435380318</v>
       </c>
       <c r="F384" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
@@ -11302,7 +11302,7 @@
         <v>3.7358727575227002</v>
       </c>
       <c r="F385" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
@@ -11322,7 +11322,7 @@
         <v>3.6824343159349202</v>
       </c>
       <c r="F386" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.3">
@@ -11342,7 +11342,7 @@
         <v>3.65566210917933</v>
       </c>
       <c r="F387" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
@@ -11362,7 +11362,7 @@
         <v>3.6330968881166799</v>
       </c>
       <c r="F388" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
@@ -11382,7 +11382,7 @@
         <v>3.61546407517063</v>
       </c>
       <c r="F389" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
@@ -11402,7 +11402,7 @@
         <v>3.60036493431268</v>
       </c>
       <c r="F390" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
@@ -11422,7 +11422,7 @@
         <v>3.5904393813006799</v>
       </c>
       <c r="F391" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
@@ -11442,7 +11442,7 @@
         <v>3.5523495762771602</v>
       </c>
       <c r="F392" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
@@ -11462,7 +11462,7 @@
         <v>3.5377287914615998</v>
       </c>
       <c r="F393" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
@@ -11482,7 +11482,7 @@
         <v>3.53156796564959</v>
       </c>
       <c r="F394" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.3">
@@ -11502,7 +11502,7 @@
         <v>3.5282158757950901</v>
       </c>
       <c r="F395" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
@@ -11522,7 +11522,7 @@
         <v>3.5163969116407801</v>
       </c>
       <c r="F396" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
@@ -11542,7 +11542,7 @@
         <v>3.47095915403087</v>
       </c>
       <c r="F397" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
@@ -11562,7 +11562,7 @@
         <v>3.4682184794634199</v>
       </c>
       <c r="F398" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
@@ -11582,7 +11582,7 @@
         <v>3.4629788249822302</v>
       </c>
       <c r="F399" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
@@ -11602,7 +11602,7 @@
         <v>3.4622494827211399</v>
       </c>
       <c r="F400" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
@@ -11622,7 +11622,7 @@
         <v>3.4583201899326901</v>
       </c>
       <c r="F401" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.3">
@@ -11642,7 +11642,7 @@
         <v>3.4327609021518999</v>
       </c>
       <c r="F402" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
@@ -11662,7 +11662,7 @@
         <v>3.40191155013177</v>
       </c>
       <c r="F403" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
@@ -11682,7 +11682,7 @@
         <v>3.36220570062344</v>
       </c>
       <c r="F404" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.3">
@@ -11702,7 +11702,7 @@
         <v>3.34823184847725</v>
       </c>
       <c r="F405" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
@@ -11722,7 +11722,7 @@
         <v>3.3355511833954798</v>
       </c>
       <c r="F406" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
@@ -11742,7 +11742,7 @@
         <v>3.3297353844779698</v>
       </c>
       <c r="F407" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
@@ -11762,7 +11762,7 @@
         <v>3.3289524747888302</v>
       </c>
       <c r="F408" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.3">
@@ -11782,7 +11782,7 @@
         <v>3.3174976099247901</v>
       </c>
       <c r="F409" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
@@ -11802,7 +11802,7 @@
         <v>3.3099813733904901</v>
       </c>
       <c r="F410" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.3">
@@ -11822,7 +11822,7 @@
         <v>3.29583686600433</v>
       </c>
       <c r="F411" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.3">
@@ -11842,7 +11842,7 @@
         <v>3.2609663084404898</v>
       </c>
       <c r="F412" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
@@ -11862,7 +11862,7 @@
         <v>3.2608648189155902</v>
       </c>
       <c r="F413" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
@@ -11882,7 +11882,7 @@
         <v>3.2392900581547899</v>
       </c>
       <c r="F414" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
@@ -11902,7 +11902,7 @@
         <v>3.23501549458478</v>
       </c>
       <c r="F415" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
@@ -11922,7 +11922,7 @@
         <v>3.20827700274473</v>
       </c>
       <c r="F416" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.3">
@@ -11942,7 +11942,7 @@
         <v>3.20808284986897</v>
       </c>
       <c r="F417" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
@@ -11962,7 +11962,7 @@
         <v>3.2011509491062502</v>
       </c>
       <c r="F418" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
@@ -11982,7 +11982,7 @@
         <v>3.1921827203040101</v>
       </c>
       <c r="F419" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
@@ -12002,7 +12002,7 @@
         <v>3.19058553639747</v>
       </c>
       <c r="F420" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
@@ -12022,7 +12022,7 @@
         <v>3.1832486472250499</v>
       </c>
       <c r="F421" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
@@ -12042,7 +12042,7 @@
         <v>3.1739301131640798</v>
       </c>
       <c r="F422" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
@@ -12062,7 +12062,7 @@
         <v>3.1735908713686798</v>
       </c>
       <c r="F423" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
@@ -12082,7 +12082,7 @@
         <v>3.1719315978584501</v>
       </c>
       <c r="F424" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
@@ -12102,7 +12102,7 @@
         <v>3.1703165511163398</v>
       </c>
       <c r="F425" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
@@ -12122,7 +12122,7 @@
         <v>3.16759096364152</v>
       </c>
       <c r="F426" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
@@ -12142,7 +12142,7 @@
         <v>3.1372318358276901</v>
       </c>
       <c r="F427" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
@@ -12162,7 +12162,7 @@
         <v>3.0979373157222398</v>
       </c>
       <c r="F428" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
@@ -12182,7 +12182,7 @@
         <v>3.0841946160253899</v>
       </c>
       <c r="F429" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
@@ -12202,7 +12202,7 @@
         <v>3.0768042786346999</v>
       </c>
       <c r="F430" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
@@ -12222,7 +12222,7 @@
         <v>3.0750751288370801</v>
       </c>
       <c r="F431" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
@@ -12242,7 +12242,7 @@
         <v>3.0747739530842</v>
       </c>
       <c r="F432" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
@@ -12262,7 +12262,7 @@
         <v>3.0726933146901199</v>
       </c>
       <c r="F433" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
@@ -12282,7 +12282,7 @@
         <v>3.0725642445244299</v>
       </c>
       <c r="F434" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
@@ -12302,7 +12302,7 @@
         <v>3.0658871263704</v>
       </c>
       <c r="F435" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
@@ -12322,7 +12322,7 @@
         <v>3.0296398518988901</v>
       </c>
       <c r="F436" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
@@ -12342,7 +12342,7 @@
         <v>2.9835789931267298</v>
       </c>
       <c r="F437" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
@@ -12362,7 +12362,7 @@
         <v>2.97778133870318</v>
       </c>
       <c r="F438" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
@@ -12382,7 +12382,7 @@
         <v>2.9760870974935201</v>
       </c>
       <c r="F439" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
@@ -12402,7 +12402,7 @@
         <v>2.9490051971460201</v>
       </c>
       <c r="F440" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
@@ -12422,7 +12422,7 @@
         <v>2.9424877590351799</v>
       </c>
       <c r="F441" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
@@ -12442,7 +12442,7 @@
         <v>2.9411816076782502</v>
       </c>
       <c r="F442" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
@@ -12462,7 +12462,7 @@
         <v>2.9406724963709601</v>
       </c>
       <c r="F443" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
@@ -12482,7 +12482,7 @@
         <v>2.93165502722441</v>
       </c>
       <c r="F444" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
@@ -12502,7 +12502,7 @@
         <v>2.9185610946143101</v>
       </c>
       <c r="F445" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
@@ -12522,7 +12522,7 @@
         <v>2.8965365394596301</v>
       </c>
       <c r="F446" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
@@ -12542,7 +12542,7 @@
         <v>2.8864154111035498</v>
       </c>
       <c r="F447" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
@@ -12562,7 +12562,7 @@
         <v>2.8657137118217402</v>
       </c>
       <c r="F448" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.3">
@@ -12582,7 +12582,7 @@
         <v>2.8398715690385101</v>
       </c>
       <c r="F449" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.3">
@@ -12602,7 +12602,7 @@
         <v>2.8266465076320002</v>
       </c>
       <c r="F450" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.3">
@@ -12622,7 +12622,7 @@
         <v>2.8215480990553101</v>
       </c>
       <c r="F451" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.3">
@@ -12642,7 +12642,7 @@
         <v>2.7642302138219601</v>
       </c>
       <c r="F452" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.3">
@@ -12662,7 +12662,7 @@
         <v>2.7507471424179601</v>
       </c>
       <c r="F453" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.3">
@@ -12682,7 +12682,7 @@
         <v>2.73332856193645</v>
       </c>
       <c r="F454" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.3">
@@ -12702,7 +12702,7 @@
         <v>2.7294578743669802</v>
       </c>
       <c r="F455" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.3">
@@ -12722,7 +12722,7 @@
         <v>2.7250329854952802</v>
       </c>
       <c r="F456" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.3">
@@ -12742,7 +12742,7 @@
         <v>2.6590727280667998</v>
       </c>
       <c r="F457" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.3">
@@ -12762,7 +12762,7 @@
         <v>2.6497191028735601</v>
       </c>
       <c r="F458" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.3">
@@ -12782,7 +12782,7 @@
         <v>2.64149268098401</v>
       </c>
       <c r="F459" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.3">
@@ -12802,7 +12802,7 @@
         <v>2.6369812049122299</v>
       </c>
       <c r="F460" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.3">
@@ -12822,7 +12822,7 @@
         <v>2.6369812049122299</v>
       </c>
       <c r="F461" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.3">
@@ -12842,7 +12842,7 @@
         <v>2.6179478736619899</v>
       </c>
       <c r="F462" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.3">
@@ -12862,7 +12862,7 @@
         <v>2.6075105599689401</v>
       </c>
       <c r="F463" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.3">
@@ -12882,7 +12882,7 @@
         <v>2.6047618707897402</v>
       </c>
       <c r="F464" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.3">
@@ -12902,7 +12902,7 @@
         <v>2.6028693780267198</v>
       </c>
       <c r="F465" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.3">
@@ -12922,7 +12922,7 @@
         <v>2.5943347504148502</v>
       </c>
       <c r="F466" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.3">
@@ -12942,7 +12942,7 @@
         <v>2.5664758908647198</v>
       </c>
       <c r="F467" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.3">
@@ -12962,7 +12962,7 @@
         <v>2.5440695332448899</v>
       </c>
       <c r="F468" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.3">
@@ -12982,7 +12982,7 @@
         <v>2.5392404975792702</v>
       </c>
       <c r="F469" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.3">
@@ -13002,7 +13002,7 @@
         <v>2.53724254194965</v>
       </c>
       <c r="F470" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.3">
@@ -13022,7 +13022,7 @@
         <v>2.5340164931152298</v>
       </c>
       <c r="F471" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.3">
@@ -13042,7 +13042,7 @@
         <v>2.4986424943073899</v>
       </c>
       <c r="F472" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.3">
@@ -13062,7 +13062,7 @@
         <v>2.4786571634568002</v>
       </c>
       <c r="F473" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.3">
@@ -13082,7 +13082,7 @@
         <v>2.47145346439099</v>
       </c>
       <c r="F474" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.3">
@@ -13102,7 +13102,7 @@
         <v>2.4650037062673</v>
       </c>
       <c r="F475" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.3">
@@ -13122,7 +13122,7 @@
         <v>2.4600687451982801</v>
       </c>
       <c r="F476" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.3">
@@ -13142,7 +13142,7 @@
         <v>2.45521117877604</v>
       </c>
       <c r="F477" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.3">
@@ -13162,7 +13162,7 @@
         <v>2.4423470353691998</v>
       </c>
       <c r="F478" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.3">
@@ -13182,7 +13182,7 @@
         <v>2.3716536019915999</v>
       </c>
       <c r="F479" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
@@ -13202,7 +13202,7 @@
         <v>2.35226053061103</v>
       </c>
       <c r="F480" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.3">
@@ -13222,7 +13222,7 @@
         <v>2.3362346334044801</v>
       </c>
       <c r="F481" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.3">
@@ -13242,7 +13242,7 @@
         <v>2.32148813955023</v>
       </c>
       <c r="F482" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.3">
@@ -13262,7 +13262,7 @@
         <v>2.29378588755241</v>
       </c>
       <c r="F483" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.3">
@@ -13282,7 +13282,7 @@
         <v>2.28267129884749</v>
       </c>
       <c r="F484" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.3">
@@ -13302,7 +13302,7 @@
         <v>2.2602789203776799</v>
       </c>
       <c r="F485" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.3">
@@ -13322,7 +13322,7 @@
         <v>2.2403359160315102</v>
       </c>
       <c r="F486" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.3">
@@ -13342,7 +13342,7 @@
         <v>2.2366610854987998</v>
       </c>
       <c r="F487" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.3">
@@ -13362,7 +13362,7 @@
         <v>2.2352423859749</v>
       </c>
       <c r="F488" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.3">
@@ -13382,7 +13382,7 @@
         <v>2.2268761781284598</v>
       </c>
       <c r="F489" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.3">
@@ -13402,7 +13402,7 @@
         <v>2.2174272846537399</v>
       </c>
       <c r="F490" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.3">
@@ -13422,7 +13422,7 @@
         <v>2.19722457733622</v>
       </c>
       <c r="F491" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.3">
@@ -13442,7 +13442,7 @@
         <v>2.1951594793232601</v>
       </c>
       <c r="F492" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.3">
@@ -13462,7 +13462,7 @@
         <v>2.1841963937076199</v>
       </c>
       <c r="F493" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.3">
@@ -13482,7 +13482,7 @@
         <v>2.1725458227851702</v>
       </c>
       <c r="F494" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.3">
@@ -13502,7 +13502,7 @@
         <v>2.1661509407115598</v>
       </c>
       <c r="F495" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.3">
@@ -13522,7 +13522,7 @@
         <v>2.16080106690712</v>
       </c>
       <c r="F496" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.3">
@@ -13542,7 +13542,7 @@
         <v>2.1594842493533699</v>
       </c>
       <c r="F497" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.3">
@@ -13562,7 +13562,7 @@
         <v>2.1525732280466499</v>
       </c>
       <c r="F498" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.3">
@@ -13582,7 +13582,7 @@
         <v>2.1495529386680099</v>
       </c>
       <c r="F499" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.3">
@@ -13602,7 +13602,7 @@
         <v>2.1165356660860799</v>
       </c>
       <c r="F500" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.3">
@@ -13622,7 +13622,7 @@
         <v>2.1131281048492201</v>
       </c>
       <c r="F501" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.3">
@@ -13642,7 +13642,7 @@
         <v>2.1110043300287602</v>
       </c>
       <c r="F502" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.3">
@@ -13662,7 +13662,7 @@
         <v>2.1080096147014298</v>
       </c>
       <c r="F503" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.3">
@@ -13682,7 +13682,7 @@
         <v>2.09567217955128</v>
       </c>
       <c r="F504" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.3">
@@ -13702,7 +13702,7 @@
         <v>2.0828814565843699</v>
       </c>
       <c r="F505" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.3">
@@ -13722,7 +13722,7 @@
         <v>2.06289457233569</v>
       </c>
       <c r="F506" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.3">
@@ -13742,7 +13742,7 @@
         <v>2.0622491411394601</v>
       </c>
       <c r="F507" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.3">
@@ -13762,7 +13762,7 @@
         <v>2.0595079135238299</v>
       </c>
       <c r="F508" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.3">
@@ -13782,7 +13782,7 @@
         <v>2.05931480767154</v>
       </c>
       <c r="F509" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.3">
@@ -13802,7 +13802,7 @@
         <v>2.0221382764028899</v>
       </c>
       <c r="F510" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.3">
@@ -13822,7 +13822,7 @@
         <v>1.9988118072797301</v>
       </c>
       <c r="F511" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.3">
@@ -13842,7 +13842,7 @@
         <v>1.98309220508432</v>
       </c>
       <c r="F512" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.3">
@@ -13862,7 +13862,7 @@
         <v>1.98100146886658</v>
       </c>
       <c r="F513" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.3">
@@ -13882,7 +13882,7 @@
         <v>1.9704151063441899</v>
       </c>
       <c r="F514" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.3">
@@ -13902,7 +13902,7 @@
         <v>1.9690522838176401</v>
       </c>
       <c r="F515" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.3">
@@ -13922,7 +13922,7 @@
         <v>1.95772638187044</v>
       </c>
       <c r="F516" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.3">
@@ -13942,7 +13942,7 @@
         <v>1.9299639013556</v>
       </c>
       <c r="F517" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.3">
@@ -13962,7 +13962,7 @@
         <v>1.8840557305372401</v>
       </c>
       <c r="F518" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.3">
@@ -13982,7 +13982,7 @@
         <v>1.8817856208857699</v>
       </c>
       <c r="F519" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.3">
@@ -14002,7 +14002,7 @@
         <v>1.87167233248666</v>
       </c>
       <c r="F520" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.3">
@@ -14022,7 +14022,7 @@
         <v>1.86685402823428</v>
       </c>
       <c r="F521" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.3">
@@ -14042,7 +14042,7 @@
         <v>1.8607689899000299</v>
       </c>
       <c r="F522" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.3">
@@ -14062,7 +14062,7 @@
         <v>1.8570013809790999</v>
       </c>
       <c r="F523" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.3">
@@ -14082,7 +14082,7 @@
         <v>1.8403084533984</v>
       </c>
       <c r="F524" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.3">
@@ -14102,7 +14102,7 @@
         <v>1.8327700675047101</v>
       </c>
       <c r="F525" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.3">
@@ -14122,7 +14122,7 @@
         <v>1.8280072596204</v>
       </c>
       <c r="F526" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.3">
@@ -14142,7 +14142,7 @@
         <v>1.82427116661468</v>
       </c>
       <c r="F527" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.3">
@@ -14162,7 +14162,7 @@
         <v>1.8191584434161701</v>
       </c>
       <c r="F528" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.3">
@@ -14182,7 +14182,7 @@
         <v>1.8108299311580001</v>
       </c>
       <c r="F529" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.3">
@@ -14202,7 +14202,7 @@
         <v>1.8050046959780801</v>
       </c>
       <c r="F530" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.3">
@@ -14222,7 +14222,7 @@
         <v>1.79732516827058</v>
       </c>
       <c r="F531" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.3">
@@ -14242,7 +14242,7 @@
         <v>1.7854503000347901</v>
       </c>
       <c r="F532" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.3">
@@ -14262,7 +14262,7 @@
         <v>1.7640648896647</v>
       </c>
       <c r="F533" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.3">
@@ -14282,7 +14282,7 @@
         <v>1.7635885922613601</v>
       </c>
       <c r="F534" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.3">
@@ -14302,7 +14302,7 @@
         <v>1.7546199222786001</v>
       </c>
       <c r="F535" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.3">
@@ -14322,7 +14322,7 @@
         <v>1.7325745326094799</v>
       </c>
       <c r="F536" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.3">
@@ -14342,7 +14342,7 @@
         <v>1.7256437599622401</v>
       </c>
       <c r="F537" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.3">
@@ -14362,7 +14362,7 @@
         <v>1.72272516537327</v>
       </c>
       <c r="F538" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
@@ -14382,7 +14382,7 @@
         <v>1.7012872055247299</v>
       </c>
       <c r="F539" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
@@ -14402,7 +14402,7 @@
         <v>1.67105159966442</v>
       </c>
       <c r="F540" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
@@ -14422,7 +14422,7 @@
         <v>1.6562217414231399</v>
       </c>
       <c r="F541" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
@@ -14442,7 +14442,7 @@
         <v>1.6453632515012899</v>
       </c>
       <c r="F542" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
@@ -14462,7 +14462,7 @@
         <v>1.64222773525709</v>
       </c>
       <c r="F543" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.3">
@@ -14482,7 +14482,7 @@
         <v>1.6368368866222101</v>
       </c>
       <c r="F544" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.3">
@@ -14502,7 +14502,7 @@
         <v>1.6282121773954801</v>
       </c>
       <c r="F545" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.3">
@@ -14522,7 +14522,7 @@
         <v>1.6262450307504801</v>
       </c>
       <c r="F546" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.3">
@@ -14542,7 +14542,7 @@
         <v>1.62270216262587</v>
       </c>
       <c r="F547" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.3">
@@ -14562,7 +14562,7 @@
         <v>1.60102035431457</v>
       </c>
       <c r="F548" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.3">
@@ -14582,7 +14582,7 @@
         <v>1.5649708196018</v>
       </c>
       <c r="F549" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.3">
@@ -14602,7 +14602,7 @@
         <v>1.5553004875852201</v>
       </c>
       <c r="F550" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
@@ -14622,7 +14622,7 @@
         <v>1.5355127439498599</v>
       </c>
       <c r="F551" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.3">
@@ -14642,7 +14642,7 @@
         <v>1.51468290923918</v>
       </c>
       <c r="F552" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.3">
@@ -14662,7 +14662,7 @@
         <v>1.49224293912927</v>
       </c>
       <c r="F553" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.3">
@@ -14682,7 +14682,7 @@
         <v>1.47810191037301</v>
       </c>
       <c r="F554" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.3">
@@ -14702,7 +14702,7 @@
         <v>1.47810191037301</v>
       </c>
       <c r="F555" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.3">
@@ -14722,7 +14722,7 @@
         <v>1.4643753222103899</v>
       </c>
       <c r="F556" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.3">
@@ -14742,7 +14742,7 @@
         <v>1.44691898293633</v>
       </c>
       <c r="F557" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.3">
@@ -14762,7 +14762,7 @@
         <v>1.4436456575913601</v>
       </c>
       <c r="F558" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.3">
@@ -14782,7 +14782,7 @@
         <v>1.44121011871601</v>
       </c>
       <c r="F559" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.3">
@@ -14802,7 +14802,7 @@
         <v>1.42172813383901</v>
       </c>
       <c r="F560" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.3">
@@ -14822,7 +14822,7 @@
         <v>1.41259706198904</v>
       </c>
       <c r="F561" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
@@ -14842,7 +14842,7 @@
         <v>1.4035876301475001</v>
       </c>
       <c r="F562" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
@@ -14862,7 +14862,7 @@
         <v>1.3913188371246099</v>
       </c>
       <c r="F563" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
@@ -14882,7 +14882,7 @@
         <v>1.3903185114196199</v>
       </c>
       <c r="F564" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
@@ -14902,7 +14902,7 @@
         <v>1.3862943611198899</v>
       </c>
       <c r="F565" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
@@ -14922,7 +14922,7 @@
         <v>1.37912587164128</v>
       </c>
       <c r="F566" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
@@ -14942,7 +14942,7 @@
         <v>1.3511623944821201</v>
       </c>
       <c r="F567" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
@@ -14962,7 +14962,7 @@
         <v>1.3245887030666199</v>
       </c>
       <c r="F568" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
@@ -14982,7 +14982,7 @@
         <v>1.3114923071603499</v>
       </c>
       <c r="F569" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.3">
@@ -15002,7 +15002,7 @@
         <v>1.30474449415578</v>
       </c>
       <c r="F570" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.3">
@@ -15022,7 +15022,7 @@
         <v>1.2970076702931299</v>
       </c>
       <c r="F571" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.3">
@@ -15042,7 +15042,7 @@
         <v>1.2910426367455601</v>
       </c>
       <c r="F572" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
@@ -15062,7 +15062,7 @@
         <v>1.2783921140191801</v>
       </c>
       <c r="F573" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
@@ -15082,7 +15082,7 @@
         <v>1.2546659186414499</v>
       </c>
       <c r="F574" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.3">
@@ -15102,7 +15102,7 @@
         <v>1.2431828745106399</v>
       </c>
       <c r="F575" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.3">
@@ -15122,7 +15122,7 @@
         <v>1.23235597298221</v>
       </c>
       <c r="F576" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.3">
@@ -15142,7 +15142,7 @@
         <v>1.19924466312999</v>
       </c>
       <c r="F577" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.3">
@@ -15162,7 +15162,7 @@
         <v>1.1856236656577399</v>
       </c>
       <c r="F578" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.3">
@@ -15182,7 +15182,7 @@
         <v>1.1741198411762499</v>
       </c>
       <c r="F579" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.3">
@@ -15202,7 +15202,7 @@
         <v>1.16587680272047</v>
       </c>
       <c r="F580" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.3">
@@ -15222,7 +15222,7 @@
         <v>1.1583840319680301</v>
       </c>
       <c r="F581" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.3">
@@ -15242,7 +15242,7 @@
         <v>1.1564318595569401</v>
       </c>
       <c r="F582" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.3">
@@ -15262,7 +15262,7 @@
         <v>1.15351458305581</v>
       </c>
       <c r="F583" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.3">
@@ -15282,7 +15282,7 @@
         <v>1.1508113306526899</v>
       </c>
       <c r="F584" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.3">
@@ -15302,7 +15302,7 @@
         <v>1.1494335717792601</v>
       </c>
       <c r="F585" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.3">
@@ -15322,7 +15322,7 @@
         <v>1.1414759930998899</v>
       </c>
       <c r="F586" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.3">
@@ -15342,7 +15342,7 @@
         <v>1.1394342831883599</v>
       </c>
       <c r="F587" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.3">
@@ -15362,7 +15362,7 @@
         <v>1.13835306394489</v>
       </c>
       <c r="F588" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.3">
@@ -15382,7 +15382,7 @@
         <v>1.12077995772408</v>
       </c>
       <c r="F589" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.3">
@@ -15402,7 +15402,7 @@
         <v>1.1141970995929</v>
       </c>
       <c r="F590" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.3">
@@ -15422,7 +15422,7 @@
         <v>1.1058325366416</v>
       </c>
       <c r="F591" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.3">
@@ -15442,7 +15442,7 @@
         <v>1.09317501918229</v>
       </c>
       <c r="F592" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.3">
@@ -15462,7 +15462,7 @@
         <v>1.09018908460552</v>
       </c>
       <c r="F593" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.3">
@@ -15482,7 +15482,7 @@
         <v>1.05458272127202</v>
       </c>
       <c r="F594" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.3">
@@ -15502,7 +15502,7 @@
         <v>1.0068047394149899</v>
       </c>
       <c r="F595" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.3">
@@ -15522,7 +15522,7 @@
         <v>1.0018517822861399</v>
       </c>
       <c r="F596" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.3">
@@ -15542,7 +15542,7 @@
         <v>0.990398704027877</v>
       </c>
       <c r="F597" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.3">
@@ -15562,7 +15562,7 @@
         <v>0.98910126628505701</v>
       </c>
       <c r="F598" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.3">
@@ -15582,7 +15582,7 @@
         <v>0.92943920471766095</v>
       </c>
       <c r="F599" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.3">
@@ -15602,7 +15602,7 @@
         <v>0.92754788639878905</v>
       </c>
       <c r="F600" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.3">
@@ -15622,7 +15622,7 @@
         <v>0.92714074789822098</v>
       </c>
       <c r="F601" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.3">
@@ -15642,7 +15642,7 @@
         <v>0.92248456645253196</v>
       </c>
       <c r="F602" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.3">
@@ -15662,7 +15662,7 @@
         <v>0.90825856017689099</v>
       </c>
       <c r="F603" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.3">
@@ -15682,7 +15682,7 @@
         <v>0.86886805332254802</v>
       </c>
       <c r="F604" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.3">
@@ -15702,7 +15702,7 @@
         <v>0.83840891296995801</v>
       </c>
       <c r="F605" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.3">
@@ -15722,7 +15722,7 @@
         <v>0.83103088792333202</v>
       </c>
       <c r="F606" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.3">
@@ -15742,7 +15742,7 @@
         <v>0.80195167016312796</v>
       </c>
       <c r="F607" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.3">
@@ -15762,7 +15762,7 @@
         <v>0.77992959361039504</v>
       </c>
       <c r="F608" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.3">
@@ -15782,7 +15782,7 @@
         <v>0.74437476976661898</v>
       </c>
       <c r="F609" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.3">
@@ -15802,7 +15802,7 @@
         <v>0.71824157816462497</v>
       </c>
       <c r="F610" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.3">
@@ -15822,7 +15822,7 @@
         <v>0.71743987312899005</v>
       </c>
       <c r="F611" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.3">
@@ -15842,7 +15842,7 @@
         <v>0.69894429824427096</v>
       </c>
       <c r="F612" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.3">
@@ -15862,7 +15862,7 @@
         <v>0.69735181184197703</v>
       </c>
       <c r="F613" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.3">
@@ -15882,7 +15882,7 @@
         <v>0.679252989949932</v>
       </c>
       <c r="F614" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.3">
@@ -15902,7 +15902,7 @@
         <v>0.59508596738373098</v>
       </c>
       <c r="F615" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
@@ -15922,7 +15922,7 @@
         <v>0.59151453501613305</v>
       </c>
       <c r="F616" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
@@ -15942,7 +15942,7 @@
         <v>0.58778666490211895</v>
       </c>
       <c r="F617" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
@@ -15962,7 +15962,7 @@
         <v>0.57804701560455996</v>
       </c>
       <c r="F618" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
@@ -15982,7 +15982,7 @@
         <v>0.57042096461854996</v>
       </c>
       <c r="F619" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.3">
@@ -16002,7 +16002,7 @@
         <v>0.54300471345435397</v>
       </c>
       <c r="F620" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.3">
@@ -16022,7 +16022,7 @@
         <v>0.52457317377158197</v>
       </c>
       <c r="F621" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
@@ -16042,7 +16042,7 @@
         <v>0.48954822531870601</v>
       </c>
       <c r="F622" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.3">
@@ -16062,7 +16062,7 @@
         <v>0.46965826574722402</v>
       </c>
       <c r="F623" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
@@ -16082,7 +16082,7 @@
         <v>0.45861922628654</v>
       </c>
       <c r="F624" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.3">
@@ -16102,7 +16102,7 @@
         <v>0.45391749149411098</v>
       </c>
       <c r="F625" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.3">
@@ -16122,7 +16122,7 @@
         <v>0.45247115048409497</v>
       </c>
       <c r="F626" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.3">
@@ -16142,7 +16142,7 @@
         <v>0.41679025746521797</v>
       </c>
       <c r="F627" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.3">
@@ -16162,7 +16162,7 @@
         <v>0.40957189006081801</v>
       </c>
       <c r="F628" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.3">
@@ -16182,7 +16182,7 @@
         <v>0.405465108108164</v>
       </c>
       <c r="F629" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.3">
@@ -16202,7 +16202,7 @@
         <v>0.391489154252191</v>
       </c>
       <c r="F630" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.3">
@@ -16222,7 +16222,7 @@
         <v>0.39049758259082801</v>
       </c>
       <c r="F631" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.3">
@@ -16242,7 +16242,7 @@
         <v>0.379756751397957</v>
       </c>
       <c r="F632" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.3">
@@ -16262,7 +16262,7 @@
         <v>0.36772478012531701</v>
       </c>
       <c r="F633" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.3">
@@ -16282,7 +16282,7 @@
         <v>0.314493329902438</v>
       </c>
       <c r="F634" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.3">
@@ -16302,7 +16302,7 @@
         <v>0.31233879432005401</v>
       </c>
       <c r="F635" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.3">
@@ -16322,7 +16322,7 @@
         <v>0.23543138210790299</v>
       </c>
       <c r="F636" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
   </sheetData>

--- a/Supplemental Files/Table S4.xlsx
+++ b/Supplemental Files/Table S4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14408950-F8A5-4551-8409-E0D01DCEDB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE47673-3EBA-43EF-A96A-C960C240B146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FA92030E-5875-45B6-8C1C-60DBF6D962C6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FA92030E-5875-45B6-8C1C-60DBF6D962C6}"/>
   </bookViews>
   <sheets>
     <sheet name="TableS4A" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="54">
   <si>
     <t>motif</t>
   </si>
@@ -113,21 +113,6 @@
   </si>
   <si>
     <t>8.41e-10</t>
-  </si>
-  <si>
-    <t>Motif 4 GAGAGAGAGAGAGAR</t>
-  </si>
-  <si>
-    <t>319 / 3073</t>
-  </si>
-  <si>
-    <t>2543 / 46643</t>
-  </si>
-  <si>
-    <t>10.4 %</t>
-  </si>
-  <si>
-    <t>3.53e-25</t>
   </si>
   <si>
     <r>
@@ -181,9 +166,6 @@
     <t>90.3 %</t>
   </si>
   <si>
-    <t>89.2 %</t>
-  </si>
-  <si>
     <t>binomial FDR</t>
   </si>
   <si>
@@ -194,9 +176,6 @@
   </si>
   <si>
     <t>2.64e-38</t>
-  </si>
-  <si>
-    <t>7.29e-44</t>
   </si>
   <si>
     <r>
@@ -226,58 +205,22 @@
     <t>module</t>
   </si>
   <si>
-    <t>4.88e-11</t>
-  </si>
-  <si>
     <t>C2H2 + ERF</t>
   </si>
   <si>
-    <t>9.28e-8</t>
-  </si>
-  <si>
     <t>ERF + MYB</t>
   </si>
   <si>
-    <t>2.79e-5</t>
-  </si>
-  <si>
     <t>C2H2 + LBD</t>
   </si>
   <si>
-    <t>3.19e-5</t>
-  </si>
-  <si>
-    <t>3.67e-5</t>
-  </si>
-  <si>
     <t>BBR-BPC + C2H2</t>
   </si>
   <si>
-    <t>1.77e-4</t>
-  </si>
-  <si>
     <t>ERF + LBD</t>
   </si>
   <si>
-    <t>0.0027</t>
-  </si>
-  <si>
-    <t>BBR-BPC + ERF</t>
-  </si>
-  <si>
     <t>0.0035</t>
-  </si>
-  <si>
-    <t>bHLH + NAC</t>
-  </si>
-  <si>
-    <t>0.016</t>
-  </si>
-  <si>
-    <t>bHLH + ERF</t>
-  </si>
-  <si>
-    <t>0.048</t>
   </si>
   <si>
     <r>
@@ -308,6 +251,21 @@
   </si>
   <si>
     <t>C2H2 + C2H2</t>
+  </si>
+  <si>
+    <t>9.54e-9</t>
+  </si>
+  <si>
+    <t>1.04e-5</t>
+  </si>
+  <si>
+    <t>2.19e-4</t>
+  </si>
+  <si>
+    <t>6.03e-4</t>
+  </si>
+  <si>
+    <t>0.0168</t>
   </si>
 </sst>
 </file>
@@ -875,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD1C54C-F17B-4715-999C-E2EBBFEF541F}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
@@ -888,7 +846,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -969,26 +927,6 @@
       </c>
       <c r="F5" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A11DBDB-F593-460F-B5C6-0FCA6D73FAF1}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -1010,7 +948,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1018,25 +956,25 @@
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -1059,10 +997,10 @@
         <v>297</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1085,10 +1023,10 @@
         <v>135</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -1111,36 +1049,10 @@
         <v>98</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="7">
-        <v>278</v>
-      </c>
-      <c r="C6" s="7">
-        <v>30</v>
-      </c>
-      <c r="D6" s="7">
-        <v>248</v>
-      </c>
-      <c r="E6" s="7">
-        <v>123</v>
-      </c>
-      <c r="F6" s="7">
-        <v>125</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1150,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717DAB3F-27DA-49C3-99E3-573E7CB18754}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
@@ -1159,12 +1071,12 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -1178,38 +1090,38 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B3" s="8">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="C3" s="8">
         <v>1356</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B4" s="7">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="C4" s="7">
         <v>1243</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="7">
         <v>50</v>
-      </c>
-      <c r="B5" s="7">
-        <v>60</v>
       </c>
       <c r="C5" s="7">
         <v>414</v>
@@ -1218,102 +1130,60 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="7">
+        <v>29</v>
+      </c>
+      <c r="C6" s="7">
+        <v>202</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="B6" s="7">
-        <v>51</v>
-      </c>
-      <c r="C6" s="7">
-        <v>330</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B7" s="7">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C7" s="7">
-        <v>648</v>
+        <v>696</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B8" s="7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7">
-        <v>202</v>
+        <v>330</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B9" s="7">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C9" s="7">
-        <v>696</v>
+        <v>648</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="7">
-        <v>32</v>
-      </c>
-      <c r="C10" s="7">
-        <v>210</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="7">
-        <v>20</v>
-      </c>
-      <c r="C11" s="7">
-        <v>114</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="7">
-        <v>48</v>
-      </c>
-      <c r="C12" s="7">
-        <v>431</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Supplemental Files/Table S4.xlsx
+++ b/Supplemental Files/Table S4.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B24511C-BB4F-4D37-B476-F102CEC5C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053E620C-169A-48ED-97A7-F862BBEBD8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TableS5" sheetId="1" r:id="rId1"/>
+    <sheet name="TableS4" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -151,38 +151,55 @@
     <t>Protein kinase</t>
   </si>
   <si>
-    <t>n = indicates the number of terms in which a gene appears.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_log2FC = is the mean log2 fold-change across pairwise contrasts, preserving direction of change. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_abs_log2FC = is the largest absolute log2 fold-change observed across contrasts. </t>
-  </si>
-  <si>
-    <t>score = combines term frequency and effect size (log1p(n) × max_abs_log2FC).</t>
+    <t>n - the number of terms in which a gene appears</t>
+  </si>
+  <si>
+    <t>mean_log2FC - the mean log2 fold-change across pairwise contrasts</t>
+  </si>
+  <si>
+    <t>max_abs_log2FC - the largest absolute log2 fold-change observed across contrasts</t>
+  </si>
+  <si>
+    <t>score - a parameter combining a GO term frequency and effect size (log1p(n) × max_abs_log2FC)</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="238"/>
       </rPr>
-      <t>Table S5</t>
+      <t>Table S4</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="238"/>
       </rPr>
-      <t xml:space="preserve">. List of putative core genes with TOP motif changes underlying GO term enrichment ranked by a combined score integrating GO term contribution and expression change. </t>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>List of genes with significant changes of the TOPscore and the top contribution to the GO term enrichment.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve"> The genes are ranked by a score combining the number of GO terms, in which a gene appears, and the magnitude of its expression change.</t>
     </r>
   </si>
 </sst>
@@ -190,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -199,16 +216,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -240,9 +261,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -554,28 +579,28 @@
     <col min="1" max="1" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
@@ -583,7 +608,7 @@
       <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -981,6 +1006,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>